--- a/salidas/exposiciones/matriz_exposiciones.xlsx
+++ b/salidas/exposiciones/matriz_exposiciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exposiciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definiciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Exposiciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Definiciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,61 +426,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K179"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MERCADO</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VALUE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>TAMANO</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>VOLATILIDAD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LIQUIDEZ</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>r2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>n_obs</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>suma_beta</t>
         </is>
@@ -481,28 +493,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01190465719782137</v>
+        <v>0.01208978360486507</v>
       </c>
       <c r="C2" t="n">
-        <v>1.311864259759288</v>
+        <v>1.306366270765871</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005983508966004801</v>
+        <v>0.003611084991778455</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3419991316405077</v>
+        <v>-0.346679091651262</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.001538300181717863</v>
+        <v>0.001985913666859992</v>
       </c>
       <c r="G2" t="n">
-        <v>0.183584001823381</v>
+        <v>0.178551753004538</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.157894338726448</v>
+        <v>-0.1438359307777857</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3852731769781914</v>
+        <v>0.3852346676254182</v>
       </c>
       <c r="J2" t="n">
         <v>190</v>
@@ -518,28 +530,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01592508271350466</v>
+        <v>0.01604726586689029</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6965772879180974</v>
+        <v>0.697793864934744</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1968604274693556</v>
+        <v>0.1822463233652546</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2098034552534228</v>
+        <v>-0.2099798179172369</v>
       </c>
       <c r="F3" t="n">
-        <v>0.017388986338673</v>
+        <v>0.01288625316880867</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1080184430723838</v>
+        <v>0.1095218283407382</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1909583104549129</v>
+        <v>0.2075315481076914</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1883689831589147</v>
+        <v>0.1882645928116514</v>
       </c>
       <c r="J3" t="n">
         <v>164</v>
@@ -555,28 +567,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003871490981383953</v>
+        <v>0.003166236666189397</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9570326476515865</v>
+        <v>0.964558906196832</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1290292713635965</v>
+        <v>-0.1094634162720474</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01163716487972514</v>
+        <v>0.0002627610649456494</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.09850742839317575</v>
+        <v>-0.09001420935555784</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4959075315866814</v>
+        <v>0.5085379461360088</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2137663146017705</v>
+        <v>-0.2738819877701812</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4454033771190814</v>
+        <v>0.4526089398811702</v>
       </c>
       <c r="J4" t="n">
         <v>190</v>
@@ -592,34 +604,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001408604019765873</v>
+        <v>0.001735721340575796</v>
       </c>
       <c r="C5" t="n">
-        <v>1.227292906291877</v>
+        <v>1.221453582942508</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2130643309832377</v>
+        <v>-0.2427265304204589</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.07267186269333184</v>
+        <v>-0.06667811166719888</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0700901310916206</v>
+        <v>-0.08468915429310854</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1338990978290043</v>
+        <v>0.1276726906720219</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.005365679352690945</v>
+        <v>0.04496752276623672</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5719677078375562</v>
+        <v>0.574085200185368</v>
       </c>
       <c r="J5" t="n">
         <v>180</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -629,28 +641,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001335603896931221</v>
+        <v>-0.002382422970259216</v>
       </c>
       <c r="C6" t="n">
-        <v>1.319029763268986</v>
+        <v>1.319080540275213</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3729864602993036</v>
+        <v>-0.3657466357135447</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1065328123382316</v>
+        <v>0.1490073402939778</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1607738558018279</v>
+        <v>0.1824839614523966</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04647586798742753</v>
+        <v>0.03733249315197884</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2598258390971691</v>
+        <v>-0.3221576994600219</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4511808254651656</v>
+        <v>0.456431308852014</v>
       </c>
       <c r="J6" t="n">
         <v>132</v>
@@ -666,34 +678,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.00565632238169864</v>
+        <v>-0.006557454150119876</v>
       </c>
       <c r="C7" t="n">
-        <v>1.051421062323629</v>
+        <v>1.048578417859231</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4814788065835483</v>
+        <v>0.390768845462006</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0535745848495745</v>
+        <v>0.1538036516712502</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1648363437603388</v>
+        <v>0.1686560924283792</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3321129368967249</v>
+        <v>-0.2887104147639434</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4191978606203655</v>
+        <v>-0.4730965926569234</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4402476306240959</v>
+        <v>0.4380900626113664</v>
       </c>
       <c r="J7" t="n">
         <v>69</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="8">
@@ -703,28 +715,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006116254859646967</v>
+        <v>0.006546681546211075</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8902252669924744</v>
+        <v>0.8831619851292125</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09984806734421822</v>
+        <v>0.08822622463145588</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1432594837211546</v>
+        <v>-0.1403598078088885</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008638506094562185</v>
+        <v>-0.01399232659716198</v>
       </c>
       <c r="G8" t="n">
-        <v>0.252221080169075</v>
+        <v>0.2524877893976695</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1076734368791752</v>
+        <v>-0.06952386475228733</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4407112650714652</v>
+        <v>0.4396639552098733</v>
       </c>
       <c r="J8" t="n">
         <v>108</v>
@@ -759,28 +771,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0007023495991080476</v>
+        <v>-0.000264837343093833</v>
       </c>
       <c r="C10" t="n">
-        <v>1.171768766612882</v>
+        <v>1.15067484111426</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2001505867773156</v>
+        <v>0.2593654013253067</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1113997067883561</v>
+        <v>0.05878863395847238</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02465325497588014</v>
+        <v>0.06620812352621103</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2712716951819421</v>
+        <v>-0.2683923530664825</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2367006199724916</v>
+        <v>-0.2666446468577675</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4025925388888948</v>
+        <v>0.4046262922777873</v>
       </c>
       <c r="J10" t="n">
         <v>72</v>
@@ -796,34 +808,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.001883714678688783</v>
+        <v>-0.001330353934290504</v>
       </c>
       <c r="C11" t="n">
-        <v>1.118081890861742</v>
+        <v>1.109696264067719</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5462053669768041</v>
+        <v>-0.5083197218042178</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7157654951831874</v>
+        <v>0.7030016784268625</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4612269568870608</v>
+        <v>0.4579266677947663</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3628802909780687</v>
+        <v>-0.3803391110971173</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3859886849771171</v>
+        <v>-0.3819657773880127</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4217060640520189</v>
+        <v>0.4204633169398462</v>
       </c>
       <c r="J11" t="n">
         <v>81</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="12">
@@ -833,28 +845,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.007640658715976676</v>
+        <v>0.006295478354508329</v>
       </c>
       <c r="C12" t="n">
-        <v>1.609201806219402</v>
+        <v>1.623291001353399</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7282893727118923</v>
+        <v>-0.8357011749091355</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3342103000980791</v>
+        <v>0.4190102284910403</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2575640232182344</v>
+        <v>0.2613267940315593</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8879929748209507</v>
+        <v>-0.8332656939340473</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4153062179971276</v>
+        <v>0.3653388449671845</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5052632628328938</v>
+        <v>0.5081271905098881</v>
       </c>
       <c r="J12" t="n">
         <v>81</v>
@@ -870,34 +882,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.004333866659955448</v>
+        <v>0.00417337619910862</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7549851311965436</v>
+        <v>0.7555647134914134</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06526057552048345</v>
+        <v>0.06809406217327832</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2400869442651486</v>
+        <v>0.2450561734627189</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.04020012125533843</v>
+        <v>-0.03209799298884164</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3223800579535816</v>
+        <v>0.3314364385841094</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3425125876804189</v>
+        <v>-0.3680533947226784</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2321038915410215</v>
+        <v>0.2349754041938577</v>
       </c>
       <c r="J13" t="n">
         <v>190</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -907,28 +919,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002239606976638167</v>
+        <v>0.002649976755354804</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8209417923964675</v>
+        <v>0.8189557931799402</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6294108645189457</v>
+        <v>-0.6178317626552275</v>
       </c>
       <c r="E14" t="n">
-        <v>0.458039875629792</v>
+        <v>0.4165567086636903</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3816905845889362</v>
+        <v>-0.388321845979447</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6410946977054299</v>
+        <v>0.6411479529075687</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0910250833761925</v>
+        <v>0.1294931538834753</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3870343138640311</v>
+        <v>0.3906731944015227</v>
       </c>
       <c r="J14" t="n">
         <v>108</v>
@@ -944,34 +956,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.002979787835087145</v>
+        <v>0.001664108397543977</v>
       </c>
       <c r="C15" t="n">
-        <v>1.343382119168522</v>
+        <v>1.350074211389221</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6976000969852517</v>
+        <v>-0.6952649227813772</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3187399796920203</v>
+        <v>0.3713012161107774</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07108543573317669</v>
+        <v>-0.06795955853908195</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08432906919753477</v>
+        <v>0.09708933473401993</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02223436466035127</v>
+        <v>-0.05524028091355926</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4160851322449637</v>
+        <v>0.4198173268765969</v>
       </c>
       <c r="J15" t="n">
         <v>190</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="16">
@@ -1000,34 +1012,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.007821372091219419</v>
+        <v>0.006423964946500412</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7358884780562346</v>
+        <v>0.7665503565120564</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4088921148945799</v>
+        <v>0.3398829828898889</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6161465297527369</v>
+        <v>-0.5234371716850071</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.02846102693060746</v>
+        <v>-0.01505986912609153</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7580577188505843</v>
+        <v>-0.7794091916278716</v>
       </c>
       <c r="H17" t="n">
-        <v>1.257884682583114</v>
+        <v>1.211472893037025</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8673119823791668</v>
+        <v>0.861620862668865</v>
       </c>
       <c r="J17" t="n">
         <v>25</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="18">
@@ -1094,34 +1106,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.02448809513952317</v>
+        <v>0.02408217655248576</v>
       </c>
       <c r="C21" t="n">
-        <v>1.116074301559935</v>
+        <v>1.122453918107504</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1623950555527499</v>
+        <v>-0.2108117296232154</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3288220735832279</v>
+        <v>-0.2979127573326655</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06928834472521458</v>
+        <v>0.04498182159982093</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.209572320260774</v>
+        <v>-0.2015627239719495</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5154268031116018</v>
+        <v>0.5428514712205055</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3483784515900031</v>
+        <v>0.3493427685398383</v>
       </c>
       <c r="J21" t="n">
         <v>129</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1131,28 +1143,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.001472906507093055</v>
+        <v>-0.001259520826537812</v>
       </c>
       <c r="C22" t="n">
-        <v>1.065328324253328</v>
+        <v>1.062796021780021</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1811804519091236</v>
+        <v>0.1970030634595195</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2254139515500956</v>
+        <v>0.2150409872399541</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1970824082371224</v>
+        <v>-0.1909198997120337</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.103202872883609</v>
+        <v>-0.1096848719656567</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1716374465918156</v>
+        <v>-0.1742353008018047</v>
       </c>
       <c r="I22" t="n">
-        <v>0.513162606995815</v>
+        <v>0.5164424170840471</v>
       </c>
       <c r="J22" t="n">
         <v>190</v>
@@ -1168,34 +1180,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.005184079776627171</v>
+        <v>-0.005093730629750953</v>
       </c>
       <c r="C23" t="n">
-        <v>1.298911681433965</v>
+        <v>1.285658453223971</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1859282935335563</v>
+        <v>0.1744411738057733</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1052398309506796</v>
+        <v>0.1338915432495557</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02041527172384969</v>
+        <v>-0.006157589377601427</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.07601645307146951</v>
+        <v>-0.08961628808555881</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.534478624570581</v>
+        <v>-0.4982172928161394</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3489406069720556</v>
+        <v>0.3487977246451823</v>
       </c>
       <c r="J23" t="n">
         <v>178</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1205,34 +1217,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0001586129287989192</v>
+        <v>0.0003281858716711693</v>
       </c>
       <c r="C24" t="n">
-        <v>1.212001598309338</v>
+        <v>1.213948160663045</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9622572782244019</v>
+        <v>1.007817286303029</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3640392683832709</v>
+        <v>-0.3979647640531719</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.001485384809669989</v>
+        <v>0.03134194504011821</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4087355430066336</v>
+        <v>-0.4095098826994258</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3999986803341654</v>
+        <v>-0.4456327452535938</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5942994734241331</v>
+        <v>0.6087384479681557</v>
       </c>
       <c r="J24" t="n">
         <v>190</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1242,28 +1254,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.00354332358857256</v>
+        <v>-0.00415916947631538</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8922785209017511</v>
+        <v>0.883783293567825</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.09341147858607252</v>
+        <v>-0.07082783301769208</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4895137144013719</v>
+        <v>0.5128980785224246</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4992240682844793</v>
+        <v>-0.5105318397526323</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3450424070948623</v>
+        <v>0.3569662892647381</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1341990955274334</v>
+        <v>-0.1722879885846634</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2304928986156741</v>
+        <v>0.2383300420835607</v>
       </c>
       <c r="J25" t="n">
         <v>37</v>
@@ -1279,28 +1291,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0004374979511440821</v>
+        <v>-0.003952118022965203</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9847141647437554</v>
+        <v>0.9758523195702169</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.160678142309846</v>
+        <v>-1.078433229325393</v>
       </c>
       <c r="E26" t="n">
-        <v>0.222124330711718</v>
+        <v>0.3151186209602757</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4828229033354287</v>
+        <v>-0.4525257850616333</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3937364292973092</v>
+        <v>0.3564912644147524</v>
       </c>
       <c r="H26" t="n">
-        <v>1.042926120892492</v>
+        <v>0.8834968094417817</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4624885452685491</v>
+        <v>0.4528362649904721</v>
       </c>
       <c r="J26" t="n">
         <v>36</v>
@@ -1316,34 +1328,34 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.001970689967928346</v>
+        <v>-0.002952711518463919</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8851648476740062</v>
+        <v>0.867202343268941</v>
       </c>
       <c r="D27" t="n">
-        <v>0.06566020613435279</v>
+        <v>0.1000237299668136</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5105516056819698</v>
+        <v>0.6016657277051537</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3971532940716707</v>
+        <v>0.3361125338063691</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.482746626721515</v>
+        <v>-0.4372765956612592</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3757833268404844</v>
+        <v>-0.4677277390860183</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2178246382535451</v>
+        <v>0.2189228189919445</v>
       </c>
       <c r="J27" t="n">
         <v>84</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1353,34 +1365,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.002790277905403647</v>
+        <v>-0.003134317519759018</v>
       </c>
       <c r="C28" t="n">
-        <v>1.221116299194081</v>
+        <v>1.220869678640863</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.151878606903872</v>
+        <v>-0.141875889589077</v>
       </c>
       <c r="E28" t="n">
-        <v>0.422338361893879</v>
+        <v>0.4347024640996213</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4092658751074715</v>
+        <v>-0.4031270287836997</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.054016268053891</v>
+        <v>-0.0516339169063119</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.02829391102272548</v>
+        <v>-0.05893530746139566</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3390761099454614</v>
+        <v>0.3413141090807166</v>
       </c>
       <c r="J28" t="n">
         <v>165</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1390,34 +1402,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0005907617801267148</v>
+        <v>0.0006596072899246672</v>
       </c>
       <c r="C29" t="n">
-        <v>1.227157015677274</v>
+        <v>1.220611047331393</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08536430242058254</v>
+        <v>0.06858833619200876</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02320963458488816</v>
+        <v>0.04622216500134842</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1376109623404677</v>
+        <v>-0.1436437255918213</v>
       </c>
       <c r="G29" t="n">
-        <v>0.08128124144064597</v>
+        <v>0.08126898034230211</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.279401231782923</v>
+        <v>-0.273046803275231</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6210988552745</v>
+        <v>0.6230078919388993</v>
       </c>
       <c r="J29" t="n">
         <v>93</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1427,28 +1439,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.001656293670404354</v>
+        <v>0.002115584444780608</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6597946695930841</v>
+        <v>0.6416478378493498</v>
       </c>
       <c r="D30" t="n">
-        <v>0.09236544799050223</v>
+        <v>0.08126335059677385</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1964138322549094</v>
+        <v>0.2082417584318781</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.02059482330205661</v>
+        <v>-0.03323718674072724</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4088118588067077</v>
+        <v>0.3964236838911023</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3367909853431468</v>
+        <v>-0.2943394440283766</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2065960290325976</v>
+        <v>0.2025891361954425</v>
       </c>
       <c r="J30" t="n">
         <v>178</v>
@@ -1464,34 +1476,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0005681823658692217</v>
+        <v>0.0005424486549807017</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9818669542314638</v>
+        <v>0.9845762013697249</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8249379322177764</v>
+        <v>0.8674846891561228</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3774214831035855</v>
+        <v>-0.4736679889292653</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07380394764836187</v>
+        <v>0.1411001841604609</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.2484704363937569</v>
+        <v>-0.2318372159765677</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2547169146002597</v>
+        <v>-0.2876558697804755</v>
       </c>
       <c r="I31" t="n">
-        <v>0.691737541728831</v>
+        <v>0.704821339757902</v>
       </c>
       <c r="J31" t="n">
         <v>49</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0.9999999999999997</v>
       </c>
     </row>
     <row r="32">
@@ -1501,28 +1513,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.005011275654369905</v>
+        <v>0.00516401320788069</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8365614924441438</v>
+        <v>0.8298885917222589</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1354204681008717</v>
+        <v>0.126079077399619</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.08334828599245189</v>
+        <v>-0.07678397550688948</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.07438850081736119</v>
+        <v>-0.08193921974454502</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2156202027227798</v>
+        <v>0.2086419124650569</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.02986537645798215</v>
+        <v>-0.005886386335500315</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5017604157707782</v>
+        <v>0.4993870899692024</v>
       </c>
       <c r="J32" t="n">
         <v>190</v>
@@ -1538,28 +1550,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.009334916501008745</v>
+        <v>0.009091583452319302</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8895053411781229</v>
+        <v>0.9033186800728527</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3723765408771181</v>
+        <v>-0.3470839073485987</v>
       </c>
       <c r="E33" t="n">
-        <v>0.07351687228216947</v>
+        <v>0.05480425799151192</v>
       </c>
       <c r="F33" t="n">
-        <v>0.07428270537649566</v>
+        <v>0.1012019931777567</v>
       </c>
       <c r="G33" t="n">
-        <v>0.491607142726345</v>
+        <v>0.490099400112102</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.156535520686015</v>
+        <v>-0.2023404240056245</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3211608906077902</v>
+        <v>0.3281181699760773</v>
       </c>
       <c r="J33" t="n">
         <v>48</v>
@@ -1575,34 +1587,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.001365856276847687</v>
+        <v>-0.001879301991222587</v>
       </c>
       <c r="C34" t="n">
-        <v>1.546633323614108</v>
+        <v>1.585585058581055</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6762902305761251</v>
+        <v>0.7086124357014454</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2431716849250392</v>
+        <v>-0.2991365260667758</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4331192036349174</v>
+        <v>-0.4482090261807973</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.5321272982019111</v>
+        <v>-0.5228593243915343</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.01450536742836511</v>
+        <v>-0.02399261764339305</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5078930176545933</v>
+        <v>0.5164679695235201</v>
       </c>
       <c r="J34" t="n">
         <v>36</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="35">
@@ -1612,28 +1624,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.003444904672134807</v>
+        <v>-0.003130284238975876</v>
       </c>
       <c r="C35" t="n">
-        <v>1.256613752095492</v>
+        <v>1.253267979321445</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9061161417804378</v>
+        <v>0.9247297252993651</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2976739513538025</v>
+        <v>-0.3175411262084965</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.03534755801880761</v>
+        <v>-0.01697428568547862</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5796762584436671</v>
+        <v>-0.5867849242266376</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2500321260596528</v>
+        <v>-0.2566973685001974</v>
       </c>
       <c r="I35" t="n">
-        <v>0.685551612821292</v>
+        <v>0.6945366706124052</v>
       </c>
       <c r="J35" t="n">
         <v>190</v>
@@ -1649,28 +1661,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.003796280563518511</v>
+        <v>0.002768729307649807</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9214936751043601</v>
+        <v>0.9290777175040554</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2410498047560047</v>
+        <v>0.1775972657124272</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1614062600153048</v>
+        <v>0.2402322677888508</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1241275562621824</v>
+        <v>0.09849563678475969</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6057956376684119</v>
+        <v>-0.592666564286668</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1577183415305599</v>
+        <v>0.1472636764965747</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4739499694263355</v>
+        <v>0.4718335936420374</v>
       </c>
       <c r="J36" t="n">
         <v>178</v>
@@ -1686,34 +1698,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.002906188673805128</v>
+        <v>0.00299762402628301</v>
       </c>
       <c r="C37" t="n">
-        <v>0.596834761322967</v>
+        <v>0.5893201879782025</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1357346035110724</v>
+        <v>0.1374463123855828</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1381977948991406</v>
+        <v>0.1490176529325742</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1958737220622482</v>
+        <v>0.1924764433797619</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3533128505327972</v>
+        <v>0.3509608372781569</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4199537323282255</v>
+        <v>-0.4192214339542782</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3728237417908724</v>
+        <v>0.37133663287156</v>
       </c>
       <c r="J37" t="n">
         <v>93</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1723,28 +1735,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.00152221741946181</v>
+        <v>-0.004053607118131228</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5763147772025603</v>
+        <v>0.5734689204568857</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1360316377771699</v>
+        <v>-0.1770440008270571</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5494444454382934</v>
+        <v>0.6739864053789267</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.08889731803607977</v>
+        <v>-0.1269974780011877</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5838402437044935</v>
+        <v>0.5378781413184375</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.4846705105320976</v>
+        <v>-0.4812919883260051</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3713628154806241</v>
+        <v>0.3829438466319094</v>
       </c>
       <c r="J38" t="n">
         <v>24</v>
@@ -1760,34 +1772,34 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.0004353456440016871</v>
+        <v>-0.0010675441763627</v>
       </c>
       <c r="C39" t="n">
-        <v>1.147778466439594</v>
+        <v>1.136714479301929</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.133489674398193</v>
+        <v>-0.1537827105736322</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3682857583021121</v>
+        <v>0.4136473752356932</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.3138942625533771</v>
+        <v>-0.3536496339709492</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3762848437558252</v>
+        <v>0.406768977762916</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.4449651315459617</v>
+        <v>-0.4496984877559567</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3743738166327563</v>
+        <v>0.3797081626782903</v>
       </c>
       <c r="J39" t="n">
         <v>72</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="40">
@@ -1797,34 +1809,34 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.002041278252493658</v>
+        <v>0.005381109655097531</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3569677226605596</v>
+        <v>0.3728517803866775</v>
       </c>
       <c r="D40" t="n">
-        <v>1.29144482778062</v>
+        <v>1.219956938637383</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.027927137034436</v>
+        <v>-0.07244531261569485</v>
       </c>
       <c r="F40" t="n">
-        <v>0.09467777062359645</v>
+        <v>-0.02449271960172372</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.2807354126027809</v>
+        <v>-0.1643192746683121</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.4344277714275589</v>
+        <v>-0.3315514121383304</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4414684550547588</v>
+        <v>0.4408436490442121</v>
       </c>
       <c r="J40" t="n">
         <v>48</v>
       </c>
       <c r="K40" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1834,28 +1846,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.001071902726716709</v>
+        <v>0.001055807892727658</v>
       </c>
       <c r="C41" t="n">
-        <v>0.927718156179598</v>
+        <v>0.9206394117057832</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.5133141281710198</v>
+        <v>-0.5177003723073581</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1657733513808802</v>
+        <v>0.1701753166235678</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.4760984339485005</v>
+        <v>-0.4915240095630007</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6380257645515602</v>
+        <v>0.6412776835463417</v>
       </c>
       <c r="H41" t="n">
-        <v>0.257895290007482</v>
+        <v>0.277131969994666</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6148760738285055</v>
+        <v>0.61821557778447</v>
       </c>
       <c r="J41" t="n">
         <v>121</v>
@@ -1871,28 +1883,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.001723028967361072</v>
+        <v>-0.00182430935972638</v>
       </c>
       <c r="C42" t="n">
-        <v>1.043436881514338</v>
+        <v>1.04222354244617</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1425289813503968</v>
+        <v>0.1301666416817424</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1588583893900245</v>
+        <v>0.173984601867365</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.4155972437248502</v>
+        <v>-0.421650466919364</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2597096711543614</v>
+        <v>0.2690487252884436</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1889366796842703</v>
+        <v>-0.1937730443643569</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4560325487462719</v>
+        <v>0.456103614465853</v>
       </c>
       <c r="J42" t="n">
         <v>181</v>
@@ -1908,28 +1920,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.01493022052411121</v>
+        <v>0.01577178524004048</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.08142594484629884</v>
+        <v>-0.1156711099038481</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6575979994308845</v>
+        <v>0.6376933403082412</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1627016522878588</v>
+        <v>-0.1599921741336829</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8220148157492737</v>
+        <v>0.8344057667498961</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2735713804311646</v>
+        <v>0.2171132001265141</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.509056598477165</v>
+        <v>-0.4135490231471206</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2954607915538551</v>
+        <v>0.2964700484220033</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
@@ -1945,28 +1957,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.00356761118393073</v>
+        <v>0.004349951405333729</v>
       </c>
       <c r="C44" t="n">
-        <v>1.296490116352493</v>
+        <v>1.32735775698318</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09138752517750853</v>
+        <v>0.2463194491061987</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.1972323026656109</v>
+        <v>-0.3559679721998087</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.1560257573093768</v>
+        <v>-0.08083869031143255</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1281618086000365</v>
+        <v>0.1111442663670022</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1627813901550508</v>
+        <v>-0.2480148099451398</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3554787603054107</v>
+        <v>0.3679922782648534</v>
       </c>
       <c r="J44" t="n">
         <v>57</v>
@@ -1982,34 +1994,34 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.002006096424739499</v>
+        <v>0.00166437656337485</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4932584900662464</v>
+        <v>0.4832536575022379</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8446283643226238</v>
+        <v>0.8514494294665149</v>
       </c>
       <c r="E45" t="n">
-        <v>0.321321948402621</v>
+        <v>0.3455235393629449</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.08739540145608961</v>
+        <v>-0.07339384663215286</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.1594359516266924</v>
+        <v>-0.1697598100576299</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4123774497087093</v>
+        <v>-0.4370729696419152</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3097483474412537</v>
+        <v>0.3156308869324074</v>
       </c>
       <c r="J45" t="n">
         <v>178</v>
       </c>
       <c r="K45" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2019,28 +2031,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.007670326506013529</v>
+        <v>0.007663914693071786</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9354119003075313</v>
+        <v>0.9250807731020256</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3316179538690845</v>
+        <v>-0.3222919176259126</v>
       </c>
       <c r="E46" t="n">
-        <v>0.127440597697256</v>
+        <v>0.1344868286101386</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.04745350754383736</v>
+        <v>-0.05381506518815089</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3712571721614062</v>
+        <v>0.3636750377146016</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.05503820875327164</v>
+        <v>-0.04713565661270232</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4143064140498771</v>
+        <v>0.4112682627513397</v>
       </c>
       <c r="J46" t="n">
         <v>190</v>
@@ -2056,34 +2068,34 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.001107063744770812</v>
+        <v>0.001016442323581227</v>
       </c>
       <c r="C47" t="n">
-        <v>1.435284988574941</v>
+        <v>1.435936282303193</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4177038789554025</v>
+        <v>-0.3415948760522578</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1294120430662172</v>
+        <v>0.07986890332385005</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.2962519536943881</v>
+        <v>-0.2477693164264367</v>
       </c>
       <c r="G47" t="n">
-        <v>0.238066827083064</v>
+        <v>0.2356642052630167</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.08880802607443126</v>
+        <v>-0.1621051984113657</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3225833917211034</v>
+        <v>0.3180569425824101</v>
       </c>
       <c r="J47" t="n">
         <v>141</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="48">
@@ -2112,34 +2124,34 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.00315786823044153</v>
+        <v>0.003225900469379675</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9325945222472475</v>
+        <v>0.9296264521418218</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2345638848805438</v>
+        <v>0.1825520692887557</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.001209492117643285</v>
+        <v>0.02766338240358308</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.01576741280558944</v>
+        <v>-0.03249254683549953</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.2189032027302361</v>
+        <v>-0.2199788304850522</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0687217005256776</v>
+        <v>0.1126294734863911</v>
       </c>
       <c r="I49" t="n">
-        <v>0.378672427805487</v>
+        <v>0.3769640418905956</v>
       </c>
       <c r="J49" t="n">
         <v>190</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2149,28 +2161,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.009443985144153403</v>
+        <v>0.007041983637236913</v>
       </c>
       <c r="C50" t="n">
-        <v>1.124790597293742</v>
+        <v>1.129507513702924</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7001508047325127</v>
+        <v>-0.6663772264611557</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03038200169164188</v>
+        <v>0.1537454560072508</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.3329561261949016</v>
+        <v>-0.3506757153853155</v>
       </c>
       <c r="G50" t="n">
-        <v>0.09030029680885335</v>
+        <v>0.08174635587113366</v>
       </c>
       <c r="H50" t="n">
-        <v>0.7876340351331775</v>
+        <v>0.6520536162651629</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5917135461380676</v>
+        <v>0.5843462099093432</v>
       </c>
       <c r="J50" t="n">
         <v>24</v>
@@ -2186,34 +2198,34 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0001118360814896219</v>
+        <v>0.0005748637119424958</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7463959226240537</v>
+        <v>0.7308543931115394</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1842438501239822</v>
+        <v>0.1961157315396571</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1064441206498903</v>
+        <v>0.1020630911460594</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1151199558269601</v>
+        <v>0.1054942811748599</v>
       </c>
       <c r="G51" t="n">
-        <v>0.08847111817764798</v>
+        <v>0.07045752847272475</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2406749674025343</v>
+        <v>-0.2049850254448405</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2338028490080698</v>
+        <v>0.2324159014050292</v>
       </c>
       <c r="J51" t="n">
         <v>166</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2223,34 +2235,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.001709789767358046</v>
+        <v>0.001860643912494033</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8887589970175449</v>
+        <v>0.8792023657680127</v>
       </c>
       <c r="D52" t="n">
-        <v>0.6829239274196024</v>
+        <v>0.6675038352681182</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.07060519626469465</v>
+        <v>-0.05368859502728537</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1999103396682639</v>
+        <v>-0.2027297995505638</v>
       </c>
       <c r="G52" t="n">
-        <v>0.01764879290930839</v>
+        <v>0.01118588903581857</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.3188161814134972</v>
+        <v>-0.3014736954941002</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4716800985420285</v>
+        <v>0.4721495038504185</v>
       </c>
       <c r="J52" t="n">
         <v>190</v>
       </c>
       <c r="K52" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2260,28 +2272,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.01039387313613668</v>
+        <v>0.01093527945422325</v>
       </c>
       <c r="C53" t="n">
-        <v>0.6045592189945456</v>
+        <v>0.5934301082603801</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3260868299270267</v>
+        <v>-0.3193931739240248</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1807726769815728</v>
+        <v>-0.2098946002334536</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3059609992424743</v>
+        <v>-0.2904937181390119</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6661627487923524</v>
+        <v>0.6532187728225567</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5420985383641759</v>
+        <v>0.5731326112135535</v>
       </c>
       <c r="I53" t="n">
-        <v>0.458940588711448</v>
+        <v>0.458622583428276</v>
       </c>
       <c r="J53" t="n">
         <v>85</v>
@@ -2297,34 +2309,34 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.003471137248425554</v>
+        <v>0.00315757802873862</v>
       </c>
       <c r="C54" t="n">
-        <v>1.124928120574376</v>
+        <v>1.121721799963837</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1894533239405576</v>
+        <v>0.1822702176462905</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.06579294215863088</v>
+        <v>-0.0215077120598391</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1450357402465135</v>
+        <v>0.1435588027910625</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.6787639817748091</v>
+        <v>-0.6945492957815055</v>
       </c>
       <c r="H54" t="n">
-        <v>0.285139739171993</v>
+        <v>0.2685061874401546</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6207988444219823</v>
+        <v>0.620915090849787</v>
       </c>
       <c r="J54" t="n">
         <v>97</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2334,34 +2346,34 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0001766993692744672</v>
+        <v>-0.0009527945932936138</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7899658312740138</v>
+        <v>0.7990093189127132</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2668609182709236</v>
+        <v>0.2288913774069337</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4046741071761688</v>
+        <v>0.4569466983623294</v>
       </c>
       <c r="F55" t="n">
-        <v>0.04539795367608165</v>
+        <v>0.02948197471097996</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.2302342234757459</v>
+        <v>-0.2136169882484182</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.276664586921442</v>
+        <v>-0.3007123811445381</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3611562712528987</v>
+        <v>0.3629206434289474</v>
       </c>
       <c r="J55" t="n">
         <v>106</v>
       </c>
       <c r="K55" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -2390,28 +2402,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.009594798116079486</v>
+        <v>0.008473758484121519</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9795540862066279</v>
+        <v>0.9985392852020318</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.2491108380598034</v>
+        <v>-0.2353517480981565</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.03054899293100904</v>
+        <v>-0.008220682511904585</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.1633354362860151</v>
+        <v>-0.1476330938224196</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1710719196289086</v>
+        <v>0.1937337399346995</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2923692614412911</v>
+        <v>0.1989324992957494</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2751999564619177</v>
+        <v>0.2729039745817868</v>
       </c>
       <c r="J57" t="n">
         <v>189</v>
@@ -2427,34 +2439,34 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.005071369642897876</v>
+        <v>-0.004727048438580401</v>
       </c>
       <c r="C58" t="n">
-        <v>1.331286734994677</v>
+        <v>1.325730593022528</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.1045079696161129</v>
+        <v>-0.08953870614039759</v>
       </c>
       <c r="E58" t="n">
-        <v>0.06926338644403196</v>
+        <v>0.05056231931070005</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2772780958207801</v>
+        <v>-0.2641853473663484</v>
       </c>
       <c r="G58" t="n">
-        <v>0.03266787992933912</v>
+        <v>0.02487647580463938</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.05143193593115512</v>
+        <v>-0.0474453346311215</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4863947885998527</v>
+        <v>0.4853480803648481</v>
       </c>
       <c r="J58" t="n">
         <v>190</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2464,34 +2476,34 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.005116954343918204</v>
+        <v>0.00494564501267687</v>
       </c>
       <c r="C59" t="n">
-        <v>0.5676861727173321</v>
+        <v>0.5644115876906818</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.3847947141094187</v>
+        <v>-0.3846481021600799</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2445953740621449</v>
+        <v>0.2538929023802431</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3558862022651147</v>
+        <v>-0.3757792659040363</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6667348628780492</v>
+        <v>0.6699363142924184</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2616645067170072</v>
+        <v>0.2721865637007729</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3725956797321243</v>
+        <v>0.3704990439229121</v>
       </c>
       <c r="J59" t="n">
         <v>120</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2520,28 +2532,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.00565646708969062</v>
+        <v>0.007513518555375655</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7640434884471912</v>
+        <v>0.7482945338693231</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.41858247870364</v>
+        <v>-0.4775939608392245</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1999401041683131</v>
+        <v>0.1876452790428516</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5862891748373412</v>
+        <v>0.5554576109664293</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.2834853125276049</v>
+        <v>-0.3021288020890456</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1517950237783994</v>
+        <v>0.2883253390496661</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2730969859973942</v>
+        <v>0.2779950890374056</v>
       </c>
       <c r="J61" t="n">
         <v>49</v>
@@ -2557,28 +2569,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.004046297407503143</v>
+        <v>0.004522520496832928</v>
       </c>
       <c r="C62" t="n">
-        <v>0.823434136094927</v>
+        <v>0.8214196030864025</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1082718050377712</v>
+        <v>0.09905858436141415</v>
       </c>
       <c r="E62" t="n">
-        <v>0.05895018548499557</v>
+        <v>0.06056860394125545</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2301574585316171</v>
+        <v>-0.253800243454288</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2974926873900976</v>
+        <v>0.307859019554052</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.05799135547617415</v>
+        <v>-0.03510556748883611</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3252515289332079</v>
+        <v>0.3267342899995802</v>
       </c>
       <c r="J62" t="n">
         <v>96</v>
@@ -2594,28 +2606,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0004459794877263862</v>
+        <v>0.002783773785059481</v>
       </c>
       <c r="C63" t="n">
-        <v>0.774478772275527</v>
+        <v>0.7176973761760131</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.5187526800819254</v>
+        <v>-0.5464937208529448</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7131239977672557</v>
+        <v>0.7280755713703598</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.4702336134505636</v>
+        <v>-0.5124636932183634</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.375983832549037</v>
+        <v>-0.3951314422026712</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8773673560387434</v>
+        <v>1.008315908727606</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6274264321794665</v>
+        <v>0.6379788835322613</v>
       </c>
       <c r="J63" t="n">
         <v>49</v>
@@ -2631,34 +2643,34 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.01782772686184123</v>
+        <v>-0.01770993660592479</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9019964766943782</v>
+        <v>0.8481639885016756</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.07783038672823811</v>
+        <v>-0.06268241678932174</v>
       </c>
       <c r="E64" t="n">
-        <v>1.863023070061213</v>
+        <v>1.905188460881807</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4114863740159994</v>
+        <v>-0.4621388516099932</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.7507611457777846</v>
+        <v>-0.7269167325477233</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.5249416402335686</v>
+        <v>-0.5016144484364446</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4352650849263218</v>
+        <v>0.4442788687418581</v>
       </c>
       <c r="J64" t="n">
         <v>60</v>
       </c>
       <c r="K64" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2687,28 +2699,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.006667651870348676</v>
+        <v>0.006138507576959027</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8614886495413511</v>
+        <v>0.8614946977153033</v>
       </c>
       <c r="D66" t="n">
-        <v>0.08040390233590811</v>
+        <v>0.01235549146252127</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.1051570301856054</v>
+        <v>-0.03431373503208907</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4729511196424023</v>
+        <v>0.463547156495541</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.02327567924960917</v>
+        <v>0.00532719675375197</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.2864109620844469</v>
+        <v>-0.3084108073950285</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4118122972648837</v>
+        <v>0.4075297674190147</v>
       </c>
       <c r="J66" t="n">
         <v>45</v>
@@ -2724,28 +2736,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.000745674629726592</v>
+        <v>-0.00186490795747463</v>
       </c>
       <c r="C67" t="n">
-        <v>0.3384371275087005</v>
+        <v>0.3569449847881754</v>
       </c>
       <c r="D67" t="n">
-        <v>0.5289202921179202</v>
+        <v>0.4925279249962439</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5902147792739871</v>
+        <v>-0.5482521216320797</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.1070347437213828</v>
+        <v>-0.0953851583087251</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4153174140573571</v>
+        <v>0.4041127516637122</v>
       </c>
       <c r="H67" t="n">
-        <v>0.4145746893113921</v>
+        <v>0.3900516184926733</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3351095207924581</v>
+        <v>0.3170631077424969</v>
       </c>
       <c r="J67" t="n">
         <v>25</v>
@@ -2761,34 +2773,34 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.01999803236927972</v>
+        <v>-0.01982730284878188</v>
       </c>
       <c r="C68" t="n">
-        <v>1.017697816286344</v>
+        <v>0.9922304306901</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3888988449350679</v>
+        <v>0.3938879847998689</v>
       </c>
       <c r="E68" t="n">
-        <v>0.730848644086236</v>
+        <v>0.7444166568553442</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.01257720441273557</v>
+        <v>-0.03198585729830557</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.3674611729732286</v>
+        <v>-0.3629059959780664</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.7574069279216837</v>
+        <v>-0.7356432190689411</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5311829279409821</v>
+        <v>0.5339618164510852</v>
       </c>
       <c r="J68" t="n">
         <v>73</v>
       </c>
       <c r="K68" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2798,28 +2810,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.001130165003891426</v>
+        <v>-0.002274501022804511</v>
       </c>
       <c r="C69" t="n">
-        <v>0.327154707040037</v>
+        <v>0.3883318696375299</v>
       </c>
       <c r="D69" t="n">
-        <v>1.232759905519386</v>
+        <v>1.102756107781511</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3395424480432227</v>
+        <v>0.435582021090866</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4373610404757797</v>
+        <v>0.3828238764300986</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.413007687215018</v>
+        <v>-1.391877974276599</v>
       </c>
       <c r="H69" t="n">
-        <v>0.07618958613659255</v>
+        <v>0.0823840993365933</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7370628060934757</v>
+        <v>0.7306284077671699</v>
       </c>
       <c r="J69" t="n">
         <v>25</v>
@@ -2835,34 +2847,34 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.009770205954091785</v>
+        <v>-0.008111867848968862</v>
       </c>
       <c r="C70" t="n">
-        <v>1.182544245515746</v>
+        <v>1.183592187623243</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.4158703567336314</v>
+        <v>-0.3204395790683719</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9962542672011042</v>
+        <v>0.8548873181413208</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.3613081428890062</v>
+        <v>-0.3797153265976393</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0257066745716398</v>
+        <v>0.1184816675310094</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.4273266876658527</v>
+        <v>-0.4568062676295622</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3884941237662453</v>
+        <v>0.3793529950405992</v>
       </c>
       <c r="J70" t="n">
         <v>37</v>
       </c>
       <c r="K70" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2872,34 +2884,34 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.02781916328001036</v>
+        <v>-0.02929582723456872</v>
       </c>
       <c r="C71" t="n">
-        <v>1.155616403009537</v>
+        <v>1.168431864382022</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.550839597185228</v>
+        <v>-0.6162471952848732</v>
       </c>
       <c r="E71" t="n">
-        <v>1.18541199079018</v>
+        <v>1.221882180295234</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.7757954959867114</v>
+        <v>-0.8481439379030007</v>
       </c>
       <c r="G71" t="n">
-        <v>0.5629027966358133</v>
+        <v>0.5831114790110941</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.577296097263591</v>
+        <v>-0.5090343905004759</v>
       </c>
       <c r="I71" t="n">
-        <v>0.61961531376</v>
+        <v>0.6198145039925191</v>
       </c>
       <c r="J71" t="n">
         <v>24</v>
       </c>
       <c r="K71" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -2909,34 +2921,34 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.01990997263806423</v>
+        <v>0.0191866584446916</v>
       </c>
       <c r="C72" t="n">
-        <v>0.866068433252881</v>
+        <v>0.8575406740353081</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.3244225222644522</v>
+        <v>-0.1252621761319306</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7989789783724555</v>
+        <v>0.6134793882629166</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.3078926885839433</v>
+        <v>-0.1981797645666388</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1057203356636884</v>
+        <v>0.1029322631791488</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.1384525364406294</v>
+        <v>-0.2505103847788041</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3168330515994281</v>
+        <v>0.2877196231759962</v>
       </c>
       <c r="J72" t="n">
         <v>24</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="73">
@@ -2946,31 +2958,31 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.003088067585545065</v>
+        <v>0.00153263823510898</v>
       </c>
       <c r="C73" t="n">
-        <v>1.184591514013226</v>
+        <v>0.8096179443680589</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.4518118913244961</v>
+        <v>-0.07356721468947705</v>
       </c>
       <c r="E73" t="n">
-        <v>0.6186313891845969</v>
+        <v>0.805341962183983</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.4621574982468776</v>
+        <v>-0.4186716086605512</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.002376661957209077</v>
+        <v>-0.3416048612548214</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1131231483307594</v>
+        <v>0.2188837780528077</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7645798198634726</v>
+        <v>0.5156097415555132</v>
       </c>
       <c r="J73" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
@@ -2983,28 +2995,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.0004169349374325874</v>
+        <v>0.0006311133638516046</v>
       </c>
       <c r="C74" t="n">
-        <v>1.196957134019506</v>
+        <v>1.195618505849705</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1785290792313947</v>
+        <v>0.2197918924475267</v>
       </c>
       <c r="E74" t="n">
-        <v>0.01602789412743379</v>
+        <v>-0.05944453483011208</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.1578076951294771</v>
+        <v>-0.1452813201506507</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.185093519556944</v>
+        <v>-0.19899805510543</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.04861289269191335</v>
+        <v>-0.01168648821103892</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3502401024887761</v>
+        <v>0.3535441765583391</v>
       </c>
       <c r="J74" t="n">
         <v>178</v>
@@ -3039,28 +3051,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.000906577482693387</v>
+        <v>-0.0001601971061003323</v>
       </c>
       <c r="C76" t="n">
-        <v>0.584486565229789</v>
+        <v>0.5798882684656328</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2778643489258555</v>
+        <v>0.2239486200000539</v>
       </c>
       <c r="E76" t="n">
-        <v>0.4476955670318984</v>
+        <v>0.5428148249344872</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1057805727962392</v>
+        <v>0.07843801519327352</v>
       </c>
       <c r="G76" t="n">
-        <v>0.07064731277229512</v>
+        <v>0.08010807976468604</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.4864743667560772</v>
+        <v>-0.5051978083581334</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1407156554235383</v>
+        <v>0.1470053427237689</v>
       </c>
       <c r="J76" t="n">
         <v>190</v>
@@ -3114,34 +3126,34 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.00781841114801291</v>
+        <v>-0.008119252396246342</v>
       </c>
       <c r="C79" t="n">
-        <v>1.278248286000967</v>
+        <v>1.191654860337069</v>
       </c>
       <c r="D79" t="n">
-        <v>0.4836883377788464</v>
+        <v>0.5427122073031367</v>
       </c>
       <c r="E79" t="n">
-        <v>0.3683119656154425</v>
+        <v>0.3527456729490034</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1695617824833112</v>
+        <v>0.3264307434030306</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.4596611594933778</v>
+        <v>-0.6946210076163594</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.840149212385189</v>
+        <v>-0.718922476375881</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5489250790631237</v>
+        <v>0.5622188509349367</v>
       </c>
       <c r="J79" t="n">
         <v>24</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0.9999999999999996</v>
       </c>
     </row>
     <row r="80">
@@ -3151,28 +3163,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.01018834138819853</v>
+        <v>0.01021674907700035</v>
       </c>
       <c r="C80" t="n">
-        <v>1.031460576605542</v>
+        <v>1.035137770945146</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.3120094575995004</v>
+        <v>-0.304732826712148</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.04764606614755445</v>
+        <v>-0.06005525565780259</v>
       </c>
       <c r="F80" t="n">
-        <v>0.08742993619792576</v>
+        <v>0.09227549956547024</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.1092547390212666</v>
+        <v>-0.1100757055583642</v>
       </c>
       <c r="H80" t="n">
-        <v>0.350019749964854</v>
+        <v>0.3474505174176986</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4052554603355242</v>
+        <v>0.4058459739922513</v>
       </c>
       <c r="J80" t="n">
         <v>190</v>
@@ -3188,34 +3200,34 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.002124799194821932</v>
+        <v>-0.001915867593285624</v>
       </c>
       <c r="C81" t="n">
-        <v>1.190100966795998</v>
+        <v>1.188306660120843</v>
       </c>
       <c r="D81" t="n">
-        <v>0.7334158356370832</v>
+        <v>0.7501822179128144</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.1043594885158155</v>
+        <v>-0.1180382453118065</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.06388045985961935</v>
+        <v>-0.05546115444165294</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.4422489275747916</v>
+        <v>-0.4437385010097568</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.3130279264828544</v>
+        <v>-0.321250977270441</v>
       </c>
       <c r="I81" t="n">
-        <v>0.6744295263789208</v>
+        <v>0.6809955538178798</v>
       </c>
       <c r="J81" t="n">
         <v>190</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="82">
@@ -3225,34 +3237,34 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.006457338553351214</v>
+        <v>0.004940831709928963</v>
       </c>
       <c r="C82" t="n">
-        <v>0.6533456489352933</v>
+        <v>0.6655757329879378</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4650774553613576</v>
+        <v>0.4261457678463632</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.1060855676991385</v>
+        <v>-0.01331985608873752</v>
       </c>
       <c r="F82" t="n">
-        <v>0.6299018800784044</v>
+        <v>0.6151989710077816</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.990248298810064</v>
+        <v>-0.9898052842698865</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3480088821341471</v>
+        <v>0.2962046685165414</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4511857654206025</v>
+        <v>0.4449363303953073</v>
       </c>
       <c r="J82" t="n">
         <v>49</v>
       </c>
       <c r="K82" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3262,28 +3274,28 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.003548792004146498</v>
+        <v>0.003192579330765345</v>
       </c>
       <c r="C83" t="n">
-        <v>1.088640288686172</v>
+        <v>1.088668660646411</v>
       </c>
       <c r="D83" t="n">
-        <v>0.03833981108353029</v>
+        <v>0.05443508886331598</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.0962438344523347</v>
+        <v>-0.08637641126391168</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1239386285145555</v>
+        <v>0.1279762368121332</v>
       </c>
       <c r="G83" t="n">
-        <v>0.2066608307738142</v>
+        <v>0.2115181511255863</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.3613357246057372</v>
+        <v>-0.3962217261835351</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4725678436568025</v>
+        <v>0.4745302661386605</v>
       </c>
       <c r="J83" t="n">
         <v>190</v>
@@ -3299,28 +3311,28 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-9.132339835288228e-06</v>
+        <v>-0.0003070410379231275</v>
       </c>
       <c r="C84" t="n">
-        <v>1.019834400009918</v>
+        <v>1.019031316437125</v>
       </c>
       <c r="D84" t="n">
-        <v>0.07114907328274678</v>
+        <v>0.0578923846682465</v>
       </c>
       <c r="E84" t="n">
-        <v>0.05972701900338802</v>
+        <v>0.08961490359522617</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.1015635811040048</v>
+        <v>-0.1150174349065213</v>
       </c>
       <c r="G84" t="n">
-        <v>0.01322615770105217</v>
+        <v>0.0158677708714338</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.06237306889310057</v>
+        <v>-0.06738894066550967</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6133356496328664</v>
+        <v>0.6145920854985608</v>
       </c>
       <c r="J84" t="n">
         <v>181</v>
@@ -3355,28 +3367,28 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.02407353898386811</v>
+        <v>-0.02366491303177008</v>
       </c>
       <c r="C86" t="n">
-        <v>1.338461711343203</v>
+        <v>1.341260109623112</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.01308551019611769</v>
+        <v>0.01597549563491302</v>
       </c>
       <c r="E86" t="n">
-        <v>0.5598686795543951</v>
+        <v>0.5217268444869699</v>
       </c>
       <c r="F86" t="n">
-        <v>0.03941634347738282</v>
+        <v>0.03607830578119198</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.3862404714190129</v>
+        <v>-0.3626394900610578</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.53842075275985</v>
+        <v>-0.5524012654651296</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3216692008959416</v>
+        <v>0.3196134904083401</v>
       </c>
       <c r="J86" t="n">
         <v>61</v>
@@ -3392,28 +3404,28 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.0003198187183582286</v>
+        <v>-0.0001324891453588641</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8164802178393957</v>
+        <v>0.8202850106571322</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2786728694030249</v>
+        <v>0.2317348090046828</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.1485484906179355</v>
+        <v>-0.102041622821727</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1536015524625223</v>
+        <v>0.1242166305106699</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.1850517347522014</v>
+        <v>-0.1790651101054378</v>
       </c>
       <c r="H87" t="n">
-        <v>0.08484558566519382</v>
+        <v>0.1048702827546799</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2890826936143854</v>
+        <v>0.2851100375135029</v>
       </c>
       <c r="J87" t="n">
         <v>190</v>
@@ -3429,28 +3441,28 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.007590236858799692</v>
+        <v>-0.006627837765905599</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8283824393809458</v>
+        <v>0.8162773761879241</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2513476807780638</v>
+        <v>0.1576552003626777</v>
       </c>
       <c r="E88" t="n">
-        <v>0.2695844139908416</v>
+        <v>0.2943622822044596</v>
       </c>
       <c r="F88" t="n">
-        <v>0.9277320538070771</v>
+        <v>0.9034062884956815</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.9810180502717281</v>
+        <v>-0.9982398754407275</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.2960285376852003</v>
+        <v>-0.1734612718100153</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3942286163349957</v>
+        <v>0.3957954815180136</v>
       </c>
       <c r="J88" t="n">
         <v>190</v>
@@ -3466,28 +3478,28 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.0009714724858431664</v>
+        <v>0.0002424161222300375</v>
       </c>
       <c r="C89" t="n">
-        <v>1.129901754282859</v>
+        <v>1.139530880824253</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.5980281060790218</v>
+        <v>-0.5809801262649307</v>
       </c>
       <c r="E89" t="n">
-        <v>0.3419201665920295</v>
+        <v>0.3499779572677204</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1271826697208764</v>
+        <v>0.1297710651826604</v>
       </c>
       <c r="G89" t="n">
-        <v>0.02357952694064265</v>
+        <v>0.02195364651854848</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.02455601145738521</v>
+        <v>-0.06025342352825142</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5914840393474725</v>
+        <v>0.592566251617446</v>
       </c>
       <c r="J89" t="n">
         <v>96</v>
@@ -3503,28 +3515,28 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.01247378375838421</v>
+        <v>0.01204817555928315</v>
       </c>
       <c r="C90" t="n">
-        <v>1.235052449020145</v>
+        <v>1.245637908788054</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.9275931792695702</v>
+        <v>-0.8995441635948684</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.133621472653452</v>
+        <v>-0.164530036620544</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.2433876782376541</v>
+        <v>-0.2278455149805976</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4589341691238077</v>
+        <v>0.4641250310124398</v>
       </c>
       <c r="H90" t="n">
-        <v>0.6106157120167233</v>
+        <v>0.5821567753955159</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5228586195462094</v>
+        <v>0.5185669895718908</v>
       </c>
       <c r="J90" t="n">
         <v>93</v>
@@ -3559,34 +3571,34 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.007668702898063598</v>
+        <v>0.007891905931713955</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6024696156448828</v>
+        <v>0.5986936185745749</v>
       </c>
       <c r="D92" t="n">
-        <v>0.01555202189806016</v>
+        <v>0.01532893415103867</v>
       </c>
       <c r="E92" t="n">
-        <v>0.01136667700630123</v>
+        <v>0.005677868578661286</v>
       </c>
       <c r="F92" t="n">
-        <v>0.01485226092423831</v>
+        <v>0.01259853849569717</v>
       </c>
       <c r="G92" t="n">
-        <v>0.2949287555323473</v>
+        <v>0.2910970389527584</v>
       </c>
       <c r="H92" t="n">
-        <v>0.06083066899417028</v>
+        <v>0.0766040012472695</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3334862053978151</v>
+        <v>0.3320848100457851</v>
       </c>
       <c r="J92" t="n">
         <v>190</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -3596,28 +3608,28 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.005546444253304328</v>
+        <v>0.00596184574783027</v>
       </c>
       <c r="C93" t="n">
-        <v>1.050896999667418</v>
+        <v>1.047150725920988</v>
       </c>
       <c r="D93" t="n">
-        <v>0.7784768410812191</v>
+        <v>0.8017601753917132</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.3193389541577847</v>
+        <v>-0.3462315534633105</v>
       </c>
       <c r="F93" t="n">
-        <v>0.03425604335825766</v>
+        <v>0.05282732370112467</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.2451992737209612</v>
+        <v>-0.2523983836644532</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.2990916562281488</v>
+        <v>-0.3031082878860624</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6225711996245248</v>
+        <v>0.6339277567721686</v>
       </c>
       <c r="J93" t="n">
         <v>190</v>
@@ -3652,28 +3664,28 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.01942978494842284</v>
+        <v>0.01939525564971894</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.2597976253061582</v>
+        <v>-0.1644229773685386</v>
       </c>
       <c r="D95" t="n">
-        <v>-1.141247918711796</v>
+        <v>-1.007795086748501</v>
       </c>
       <c r="E95" t="n">
-        <v>0.849534504031094</v>
+        <v>0.7525720679959109</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9516161120989324</v>
+        <v>0.970834659859766</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.03222272923539411</v>
+        <v>-0.01244870928430797</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6321176571233219</v>
+        <v>0.4612600455456712</v>
       </c>
       <c r="I95" t="n">
-        <v>0.545717515008844</v>
+        <v>0.5313418688121216</v>
       </c>
       <c r="J95" t="n">
         <v>33</v>
@@ -3689,34 +3701,34 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.00437088436647117</v>
+        <v>0.003597944691327186</v>
       </c>
       <c r="C96" t="n">
-        <v>0.9012605416589958</v>
+        <v>0.9309324860766633</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.3098379910216412</v>
+        <v>-0.3392602487144886</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.1702144469563588</v>
+        <v>-0.1552390410464777</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.1097914694236591</v>
+        <v>-0.1088596359725389</v>
       </c>
       <c r="G96" t="n">
-        <v>0.6964370802354773</v>
+        <v>0.7035490858417349</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.007853714492814188</v>
+        <v>-0.03112264618489317</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4858222025532499</v>
+        <v>0.4927801516025269</v>
       </c>
       <c r="J96" t="n">
         <v>49</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -3726,34 +3738,34 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.03292266951587288</v>
+        <v>-0.03871639099334515</v>
       </c>
       <c r="C97" t="n">
-        <v>1.071174436823771</v>
+        <v>1.18510560579557</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.5555819342058814</v>
+        <v>-0.6885265824245907</v>
       </c>
       <c r="E97" t="n">
-        <v>1.80469994795623</v>
+        <v>2.097638400591654</v>
       </c>
       <c r="F97" t="n">
-        <v>-2.304453121740892</v>
+        <v>-2.302687467174114</v>
       </c>
       <c r="G97" t="n">
-        <v>0.4547133192647839</v>
+        <v>0.3890623252787565</v>
       </c>
       <c r="H97" t="n">
-        <v>0.529447351901989</v>
+        <v>0.3194077179327236</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3314930868163215</v>
+        <v>0.3521446337427125</v>
       </c>
       <c r="J97" t="n">
         <v>24</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="98">
@@ -3763,28 +3775,28 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.004148516206640469</v>
+        <v>0.004620632613010055</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6345096134778369</v>
+        <v>0.6275719730313045</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.1380350736126498</v>
+        <v>-0.1538741910682099</v>
       </c>
       <c r="E98" t="n">
-        <v>0.160097521163719</v>
+        <v>0.1587014315631701</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.09288430273952035</v>
+        <v>-0.1129928712672252</v>
       </c>
       <c r="G98" t="n">
-        <v>0.36777029331634</v>
+        <v>0.3608444913006438</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0685419483942743</v>
+        <v>0.1197491664403167</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3906083354363844</v>
+        <v>0.3882850730119097</v>
       </c>
       <c r="J98" t="n">
         <v>190</v>
@@ -3800,34 +3812,34 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.0004684156323916079</v>
+        <v>0.0004025732577499219</v>
       </c>
       <c r="C99" t="n">
-        <v>0.8947285469497093</v>
+        <v>0.8906842914385719</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1099480019324305</v>
+        <v>0.09542197956306672</v>
       </c>
       <c r="E99" t="n">
-        <v>0.04344792566307003</v>
+        <v>0.06427432597234661</v>
       </c>
       <c r="F99" t="n">
-        <v>0.09361140332754629</v>
+        <v>0.08669198408099564</v>
       </c>
       <c r="G99" t="n">
-        <v>0.1875619470840335</v>
+        <v>0.1873166671030402</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.3292978249567897</v>
+        <v>-0.3243892481580211</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4684510556920645</v>
+        <v>0.4673740431072945</v>
       </c>
       <c r="J99" t="n">
         <v>130</v>
       </c>
       <c r="K99" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -3837,28 +3849,28 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.02304357740529518</v>
+        <v>0.02331500661919204</v>
       </c>
       <c r="C100" t="n">
-        <v>0.5153003988821606</v>
+        <v>0.519031373468907</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.2296120624891213</v>
+        <v>-0.2248615146597117</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.1596987013569646</v>
+        <v>-0.1810339633590397</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2757449996431434</v>
+        <v>0.2812341656732413</v>
       </c>
       <c r="G100" t="n">
-        <v>0.2819907796483185</v>
+        <v>0.273541789617835</v>
       </c>
       <c r="H100" t="n">
-        <v>0.3162745856724634</v>
+        <v>0.3320881492587682</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1336375080339274</v>
+        <v>0.1350741098625351</v>
       </c>
       <c r="J100" t="n">
         <v>190</v>
@@ -3874,28 +3886,28 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.002704744373187063</v>
+        <v>0.002173848551001068</v>
       </c>
       <c r="C101" t="n">
-        <v>0.696954804669479</v>
+        <v>0.6942498525768135</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1880900793157703</v>
+        <v>0.1596958999699553</v>
       </c>
       <c r="E101" t="n">
-        <v>0.305962575276102</v>
+        <v>0.3732257859633075</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.1011451827582137</v>
+        <v>-0.1351305968386483</v>
       </c>
       <c r="G101" t="n">
-        <v>0.4299878519201789</v>
+        <v>0.4580196836493548</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.5198501284233165</v>
+        <v>-0.5500606253207827</v>
       </c>
       <c r="I101" t="n">
-        <v>0.3306705060926408</v>
+        <v>0.3406886297895664</v>
       </c>
       <c r="J101" t="n">
         <v>132</v>
@@ -3911,28 +3923,28 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.0004293363808266284</v>
+        <v>0.0005907345154529301</v>
       </c>
       <c r="C102" t="n">
-        <v>1.228135763779571</v>
+        <v>1.225107738028277</v>
       </c>
       <c r="D102" t="n">
-        <v>0.04348117812654629</v>
+        <v>0.06829531085255225</v>
       </c>
       <c r="E102" t="n">
-        <v>0.01759388605002526</v>
+        <v>-0.001259323351362028</v>
       </c>
       <c r="F102" t="n">
-        <v>0.09590439038458626</v>
+        <v>0.1043030888812992</v>
       </c>
       <c r="G102" t="n">
-        <v>0.1690435044163786</v>
+        <v>0.1759772046390348</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.5541587227571072</v>
+        <v>-0.5724240190498011</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4403815950799546</v>
+        <v>0.4426790205271515</v>
       </c>
       <c r="J102" t="n">
         <v>181</v>
@@ -3948,28 +3960,28 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.006793581349074285</v>
+        <v>0.007026835091879007</v>
       </c>
       <c r="C103" t="n">
-        <v>0.8074945924393642</v>
+        <v>0.7791912842738344</v>
       </c>
       <c r="D103" t="n">
-        <v>0.115789850481843</v>
+        <v>0.1358822358824534</v>
       </c>
       <c r="E103" t="n">
-        <v>0.3995445812951987</v>
+        <v>0.3916525472713526</v>
       </c>
       <c r="F103" t="n">
-        <v>0.4349901611362486</v>
+        <v>0.4352805407209309</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.9536448135822344</v>
+        <v>-0.9723355222316195</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1958256282295799</v>
+        <v>0.2303289140830482</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5385622278487763</v>
+        <v>0.5425010039984868</v>
       </c>
       <c r="J103" t="n">
         <v>57</v>
@@ -4004,28 +4016,28 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.006973252690361398</v>
+        <v>0.006974716608726968</v>
       </c>
       <c r="C105" t="n">
-        <v>1.057042803928124</v>
+        <v>1.052499654811155</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.1855274014361858</v>
+        <v>-0.1828628915417101</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2306420626763259</v>
+        <v>0.2370494495202589</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.2056144234368929</v>
+        <v>-0.2048619124682255</v>
       </c>
       <c r="G105" t="n">
-        <v>0.2650889561178381</v>
+        <v>0.2637149899203972</v>
       </c>
       <c r="H105" t="n">
-        <v>-0.1616319978492091</v>
+        <v>-0.1655392902418758</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4570771076633424</v>
+        <v>0.4571753580679196</v>
       </c>
       <c r="J105" t="n">
         <v>189</v>
@@ -4041,28 +4053,28 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.005560367709348521</v>
+        <v>0.005522568507400247</v>
       </c>
       <c r="C106" t="n">
-        <v>0.7004418828735322</v>
+        <v>0.7006489940621612</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.1335767135645311</v>
+        <v>-0.1289591356733132</v>
       </c>
       <c r="E106" t="n">
-        <v>0.04427138275725725</v>
+        <v>0.04389521476029107</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.1085472427257799</v>
+        <v>-0.1130670068506991</v>
       </c>
       <c r="G106" t="n">
-        <v>0.399420446533056</v>
+        <v>0.4000768576752232</v>
       </c>
       <c r="H106" t="n">
-        <v>0.09799024412646561</v>
+        <v>0.0974050760263369</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3836533043163699</v>
+        <v>0.3828584652961069</v>
       </c>
       <c r="J106" t="n">
         <v>190</v>
@@ -4078,34 +4090,34 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.0001296731404971633</v>
+        <v>0.001130472584576137</v>
       </c>
       <c r="C107" t="n">
-        <v>0.5291957768106255</v>
+        <v>0.5087894120928083</v>
       </c>
       <c r="D107" t="n">
-        <v>0.214489319446787</v>
+        <v>0.2458632964093388</v>
       </c>
       <c r="E107" t="n">
-        <v>0.4010097172927816</v>
+        <v>0.3195582297451421</v>
       </c>
       <c r="F107" t="n">
-        <v>0.6266923477618789</v>
+        <v>0.6423113742464605</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.1989922928415765</v>
+        <v>-0.1726854091877623</v>
       </c>
       <c r="H107" t="n">
-        <v>-0.5723948684704965</v>
+        <v>-0.5438369033059873</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2099959169293025</v>
+        <v>0.2029552722169493</v>
       </c>
       <c r="J107" t="n">
         <v>24</v>
       </c>
       <c r="K107" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="108">
@@ -4115,34 +4127,34 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.004295381529218358</v>
+        <v>0.004188406531294596</v>
       </c>
       <c r="C108" t="n">
-        <v>0.8381762649908981</v>
+        <v>0.829304519951489</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.1321988113454332</v>
+        <v>-0.1327668373888737</v>
       </c>
       <c r="E108" t="n">
-        <v>0.08327052674701026</v>
+        <v>0.09985372204260655</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.2450186200732828</v>
+        <v>-0.2482381880476525</v>
       </c>
       <c r="G108" t="n">
-        <v>0.5004689264892209</v>
+        <v>0.4942054829670322</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.04469828680841333</v>
+        <v>-0.04235869952460167</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4494475000203482</v>
+        <v>0.4467545701559108</v>
       </c>
       <c r="J108" t="n">
         <v>157</v>
       </c>
       <c r="K108" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="109">
@@ -4152,28 +4164,28 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-0.000366451835454558</v>
+        <v>-0.0004179973376138535</v>
       </c>
       <c r="C109" t="n">
-        <v>0.8211352192789957</v>
+        <v>0.821356733890684</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.3717924672737948</v>
+        <v>-0.3532708968081257</v>
       </c>
       <c r="E109" t="n">
-        <v>0.3884377139178085</v>
+        <v>0.3818153450137328</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.2720907924784403</v>
+        <v>-0.2727353696430091</v>
       </c>
       <c r="G109" t="n">
-        <v>0.3018136712623943</v>
+        <v>0.3028620273697542</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1324966552930366</v>
+        <v>0.1199721601769638</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4012253051083073</v>
+        <v>0.3997154979938263</v>
       </c>
       <c r="J109" t="n">
         <v>190</v>
@@ -4189,34 +4201,34 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-0.005797268785239733</v>
+        <v>-0.00443950136592061</v>
       </c>
       <c r="C110" t="n">
-        <v>1.317631730666645</v>
+        <v>1.283132212535511</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4577029996538484</v>
+        <v>0.4941413187215936</v>
       </c>
       <c r="E110" t="n">
-        <v>0.1429534647651191</v>
+        <v>0.07686749276615504</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.1797388959229093</v>
+        <v>-0.1455197261130068</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.6110311938088936</v>
+        <v>-0.62686958393053</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.1275181053538091</v>
+        <v>-0.08175171397972239</v>
       </c>
       <c r="I110" t="n">
-        <v>0.732496239782098</v>
+        <v>0.7354958068761401</v>
       </c>
       <c r="J110" t="n">
         <v>85</v>
       </c>
       <c r="K110" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -4226,28 +4238,28 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.01009325482023869</v>
+        <v>0.0109103570788088</v>
       </c>
       <c r="C111" t="n">
-        <v>1.202050667665739</v>
+        <v>1.206835864576601</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.3343305394104932</v>
+        <v>-0.3204400702100298</v>
       </c>
       <c r="E111" t="n">
-        <v>0.01322974993774746</v>
+        <v>-0.04198017200752462</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.02382463432765193</v>
+        <v>0.005797069225276751</v>
       </c>
       <c r="G111" t="n">
-        <v>-0.04743929277116884</v>
+        <v>-0.04677355424913182</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1903140489058279</v>
+        <v>0.1965608626648081</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2707071922876333</v>
+        <v>0.2660119037361575</v>
       </c>
       <c r="J111" t="n">
         <v>153</v>
@@ -4263,34 +4275,34 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.001091062009891546</v>
+        <v>0.001202062526432929</v>
       </c>
       <c r="C112" t="n">
-        <v>0.9568768229296608</v>
+        <v>0.9491132457732124</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.0365559391572312</v>
+        <v>-0.05291308803904343</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.05050214681284466</v>
+        <v>-0.03504210435578959</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.1385361120924064</v>
+        <v>-0.1394934948540974</v>
       </c>
       <c r="G112" t="n">
-        <v>0.06311545957305222</v>
+        <v>0.04611130785789405</v>
       </c>
       <c r="H112" t="n">
-        <v>0.2056019155597693</v>
+        <v>0.232224133617824</v>
       </c>
       <c r="I112" t="n">
-        <v>0.557568794681671</v>
+        <v>0.5586096190627665</v>
       </c>
       <c r="J112" t="n">
         <v>133</v>
       </c>
       <c r="K112" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -4300,28 +4312,28 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.007668908267671064</v>
+        <v>0.008656806327811351</v>
       </c>
       <c r="C113" t="n">
-        <v>0.6252227218624677</v>
+        <v>0.6089742828591643</v>
       </c>
       <c r="D113" t="n">
-        <v>0.1446618765358528</v>
+        <v>0.1312106837156058</v>
       </c>
       <c r="E113" t="n">
-        <v>0.0001086904552856247</v>
+        <v>-0.01289657127567845</v>
       </c>
       <c r="F113" t="n">
-        <v>0.04858525495628913</v>
+        <v>0.02805525360285487</v>
       </c>
       <c r="G113" t="n">
-        <v>0.2509208027081106</v>
+        <v>0.2317248458775337</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.06949934651800582</v>
+        <v>0.01293150522051972</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1799409625330687</v>
+        <v>0.175407845135931</v>
       </c>
       <c r="J113" t="n">
         <v>166</v>
@@ -4356,28 +4368,28 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.0122041104208253</v>
+        <v>0.01188475085103006</v>
       </c>
       <c r="C115" t="n">
-        <v>0.4578682792471133</v>
+        <v>0.4652388722005782</v>
       </c>
       <c r="D115" t="n">
-        <v>0.07251702929103611</v>
+        <v>0.06574806002940503</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.03428056870870961</v>
+        <v>-0.02463841844254845</v>
       </c>
       <c r="F115" t="n">
-        <v>0.009969070177628277</v>
+        <v>0.007091796376700356</v>
       </c>
       <c r="G115" t="n">
-        <v>0.1903450692610397</v>
+        <v>0.1949424626583894</v>
       </c>
       <c r="H115" t="n">
-        <v>0.3035811207318923</v>
+        <v>0.2916172271774753</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1416232856690448</v>
+        <v>0.1394393107603473</v>
       </c>
       <c r="J115" t="n">
         <v>190</v>
@@ -4412,34 +4424,34 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.007491176003931556</v>
+        <v>0.008015448779162472</v>
       </c>
       <c r="C117" t="n">
-        <v>0.8768990212831351</v>
+        <v>0.8812992373913238</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.604448647137526</v>
+        <v>-0.5476875989074411</v>
       </c>
       <c r="E117" t="n">
-        <v>0.449524945269571</v>
+        <v>0.3905205610233802</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.1747739922286664</v>
+        <v>-0.1737479195904006</v>
       </c>
       <c r="G117" t="n">
-        <v>0.645280702099877</v>
+        <v>0.6185630138813532</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.1924820292863906</v>
+        <v>-0.1689472937982154</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7158326134541313</v>
+        <v>0.7187586987361616</v>
       </c>
       <c r="J117" t="n">
         <v>36</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="118">
@@ -4468,34 +4480,34 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.001153846632149145</v>
+        <v>0.0006490839022657803</v>
       </c>
       <c r="C119" t="n">
-        <v>1.09353864653781</v>
+        <v>1.101141051015402</v>
       </c>
       <c r="D119" t="n">
-        <v>0.7425697034933902</v>
+        <v>0.7608347032834565</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.05464241278701856</v>
+        <v>-0.05642115398091241</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.09056158720006982</v>
+        <v>-0.07199338285890877</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.5439508591665922</v>
+        <v>-0.536707779273066</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.14695349087752</v>
+        <v>-0.1968534381859713</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6165567163827721</v>
+        <v>0.6227278699145479</v>
       </c>
       <c r="J119" t="n">
         <v>142</v>
       </c>
       <c r="K119" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -4505,28 +4517,28 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.01439148647159592</v>
+        <v>0.01393649731676332</v>
       </c>
       <c r="C120" t="n">
-        <v>1.034510283404102</v>
+        <v>1.04616608614535</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.1266416414283062</v>
+        <v>-0.1241194078983864</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.1670770081352752</v>
+        <v>-0.1685865851673192</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.1798597601739513</v>
+        <v>-0.1686333538142986</v>
       </c>
       <c r="G120" t="n">
-        <v>0.06056093641836081</v>
+        <v>0.0710128883725147</v>
       </c>
       <c r="H120" t="n">
-        <v>0.3785071899150696</v>
+        <v>0.3441603723621391</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3996301793468192</v>
+        <v>0.3968978177420334</v>
       </c>
       <c r="J120" t="n">
         <v>190</v>
@@ -4542,34 +4554,34 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-0.008575789844583926</v>
+        <v>-0.008994304971972206</v>
       </c>
       <c r="C121" t="n">
-        <v>1.625602312970634</v>
+        <v>1.611762636687792</v>
       </c>
       <c r="D121" t="n">
-        <v>1.242106548863507</v>
+        <v>1.242490486835137</v>
       </c>
       <c r="E121" t="n">
-        <v>0.4618657067322117</v>
+        <v>0.4775134628961106</v>
       </c>
       <c r="F121" t="n">
-        <v>0.3205711807583095</v>
+        <v>0.3558065602031044</v>
       </c>
       <c r="G121" t="n">
-        <v>-2.210358986478446</v>
+        <v>-2.21146919811265</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.439786762846216</v>
+        <v>-0.4761039485094941</v>
       </c>
       <c r="I121" t="n">
-        <v>0.665716584830088</v>
+        <v>0.66498694937008</v>
       </c>
       <c r="J121" t="n">
         <v>45</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -4579,28 +4591,28 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.005162331429145841</v>
+        <v>0.00504423582863171</v>
       </c>
       <c r="C122" t="n">
-        <v>0.6573857981775937</v>
+        <v>0.6501793979232771</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.4739961738046484</v>
+        <v>-0.4945315105400375</v>
       </c>
       <c r="E122" t="n">
-        <v>0.3694497806300115</v>
+        <v>0.3966257842818385</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.008855077955509339</v>
+        <v>-0.03943666840916521</v>
       </c>
       <c r="G122" t="n">
-        <v>0.5350384920979263</v>
+        <v>0.5375267907533918</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.0790228191453738</v>
+        <v>-0.05036379400930464</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2855722265760462</v>
+        <v>0.295876583754683</v>
       </c>
       <c r="J122" t="n">
         <v>141</v>
@@ -4635,34 +4647,34 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.002343170762534054</v>
+        <v>0.001187057627483631</v>
       </c>
       <c r="C124" t="n">
-        <v>1.472041532522266</v>
+        <v>1.467472864285901</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.778368836488134</v>
+        <v>-0.7177707048761548</v>
       </c>
       <c r="E124" t="n">
-        <v>0.5551276558319628</v>
+        <v>0.5899314845392195</v>
       </c>
       <c r="F124" t="n">
-        <v>0.004261329662523316</v>
+        <v>0.02332813289192469</v>
       </c>
       <c r="G124" t="n">
-        <v>0.4789103094817101</v>
+        <v>0.4677546926395508</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.7319719910103282</v>
+        <v>-0.8307164694804414</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2628924345697176</v>
+        <v>0.2686409767566028</v>
       </c>
       <c r="J124" t="n">
         <v>129</v>
       </c>
       <c r="K124" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="125">
@@ -4672,28 +4684,28 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.002418804001346294</v>
+        <v>-0.002065926040152725</v>
       </c>
       <c r="C125" t="n">
-        <v>0.9841678853244928</v>
+        <v>0.9875410104217787</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.3275797918383646</v>
+        <v>-0.3157876681827515</v>
       </c>
       <c r="E125" t="n">
-        <v>0.4193723626441753</v>
+        <v>0.3891596260407715</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.2317764656676698</v>
+        <v>-0.2449775601447651</v>
       </c>
       <c r="G125" t="n">
-        <v>0.1842953138849132</v>
+        <v>0.19600414910735</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.0284793043475469</v>
+        <v>-0.01193955724238363</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2922514448224417</v>
+        <v>0.2920423852175741</v>
       </c>
       <c r="J125" t="n">
         <v>169</v>
@@ -4709,28 +4721,28 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.02372529019543078</v>
+        <v>0.0240458102001497</v>
       </c>
       <c r="C126" t="n">
-        <v>0.4879285096110808</v>
+        <v>0.4882267099916106</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.009409392906074175</v>
+        <v>0.03788958763043954</v>
       </c>
       <c r="E126" t="n">
-        <v>0.2951150093315372</v>
+        <v>0.2305327073065636</v>
       </c>
       <c r="F126" t="n">
-        <v>0.3646163348227207</v>
+        <v>0.4170405245066537</v>
       </c>
       <c r="G126" t="n">
-        <v>0.2566900939799024</v>
+        <v>0.2211859222024467</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.3949405548391669</v>
+        <v>-0.3948754516377142</v>
       </c>
       <c r="I126" t="n">
-        <v>0.2031625138760925</v>
+        <v>0.2000467985496851</v>
       </c>
       <c r="J126" t="n">
         <v>24</v>
@@ -4765,28 +4777,28 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.004084975043580385</v>
+        <v>0.003577574886539713</v>
       </c>
       <c r="C128" t="n">
-        <v>1.190467966943645</v>
+        <v>1.211771609696389</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.8506296182316148</v>
+        <v>-0.721563299018372</v>
       </c>
       <c r="E128" t="n">
-        <v>0.4582794410773134</v>
+        <v>0.3799209776204112</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.3231197773807163</v>
+        <v>-0.2777213558714391</v>
       </c>
       <c r="G128" t="n">
-        <v>0.3358405179245399</v>
+        <v>0.3263966697734555</v>
       </c>
       <c r="H128" t="n">
-        <v>0.1891614696668327</v>
+        <v>0.08119539779955587</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2497632839113773</v>
+        <v>0.2373735709678212</v>
       </c>
       <c r="J128" t="n">
         <v>81</v>
@@ -4802,34 +4814,34 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.01760654401089189</v>
+        <v>0.01694664807472365</v>
       </c>
       <c r="C129" t="n">
-        <v>1.914673060059896</v>
+        <v>1.902911732895357</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.6999205925670464</v>
+        <v>-0.6414017486990692</v>
       </c>
       <c r="E129" t="n">
-        <v>0.2130753216962527</v>
+        <v>0.2108105246462617</v>
       </c>
       <c r="F129" t="n">
-        <v>0.01887223106896312</v>
+        <v>0.04835320703401458</v>
       </c>
       <c r="G129" t="n">
-        <v>0.1279033133224561</v>
+        <v>0.1116241696009296</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.5746033335805221</v>
+        <v>-0.6322978854774935</v>
       </c>
       <c r="I129" t="n">
-        <v>0.440400347171606</v>
+        <v>0.4397801921134921</v>
       </c>
       <c r="J129" t="n">
         <v>117</v>
       </c>
       <c r="K129" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -4839,28 +4851,28 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.004428397520672971</v>
+        <v>0.003683452184662884</v>
       </c>
       <c r="C130" t="n">
-        <v>1.056772755939395</v>
+        <v>1.071383982274454</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.1720723689124275</v>
+        <v>-0.1817580664555887</v>
       </c>
       <c r="E130" t="n">
-        <v>0.04450820623044299</v>
+        <v>0.05504550830308225</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.1689062723793302</v>
+        <v>-0.1677017602806956</v>
       </c>
       <c r="G130" t="n">
-        <v>-0.3881179854947999</v>
+        <v>-0.3788013240853739</v>
       </c>
       <c r="H130" t="n">
-        <v>0.6278156646167196</v>
+        <v>0.6018316602441216</v>
       </c>
       <c r="I130" t="n">
-        <v>0.397711995799455</v>
+        <v>0.3955038982998914</v>
       </c>
       <c r="J130" t="n">
         <v>190</v>
@@ -4876,34 +4888,34 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.001399677151156059</v>
+        <v>-0.002472381713741388</v>
       </c>
       <c r="C131" t="n">
-        <v>0.9364403012745661</v>
+        <v>0.9479394696824304</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.4636662358020232</v>
+        <v>-0.447046677404956</v>
       </c>
       <c r="E131" t="n">
-        <v>0.4236380825649591</v>
+        <v>0.4814223267002873</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.3666658503784061</v>
+        <v>-0.3641336559562051</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.6664321429039094</v>
+        <v>-0.6687778680757654</v>
       </c>
       <c r="H131" t="n">
-        <v>1.136685845244813</v>
+        <v>1.050596405054209</v>
       </c>
       <c r="I131" t="n">
-        <v>0.5152927342841666</v>
+        <v>0.5091299081695392</v>
       </c>
       <c r="J131" t="n">
         <v>85</v>
       </c>
       <c r="K131" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -4913,34 +4925,34 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.006646803321871024</v>
+        <v>0.006887130475634095</v>
       </c>
       <c r="C132" t="n">
-        <v>0.6823273849179823</v>
+        <v>0.7469805500033996</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.6686477221156997</v>
+        <v>-0.3776986253113016</v>
       </c>
       <c r="E132" t="n">
-        <v>0.8017899149676105</v>
+        <v>0.5608797781289805</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.07643972215689099</v>
+        <v>-0.01107086171211343</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.4072272254014721</v>
+        <v>-0.4654200912054682</v>
       </c>
       <c r="H132" t="n">
-        <v>0.66819736978847</v>
+        <v>0.5463292500965031</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2337207945812564</v>
+        <v>0.218044483934638</v>
       </c>
       <c r="J132" t="n">
         <v>33</v>
       </c>
       <c r="K132" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="133">
@@ -4950,28 +4962,28 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.003523407312801844</v>
+        <v>0.003351422244258843</v>
       </c>
       <c r="C133" t="n">
-        <v>0.6742745148766571</v>
+        <v>0.6676449776468769</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.1050084136868132</v>
+        <v>-0.1155884948631274</v>
       </c>
       <c r="E133" t="n">
-        <v>0.07549217636548676</v>
+        <v>0.09649785565356321</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.1300264627017111</v>
+        <v>-0.1428655767386262</v>
       </c>
       <c r="G133" t="n">
-        <v>0.422967496378722</v>
+        <v>0.4206908075128108</v>
       </c>
       <c r="H133" t="n">
-        <v>0.06230068876765845</v>
+        <v>0.07362043078850261</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4672189379904419</v>
+        <v>0.4672959198321389</v>
       </c>
       <c r="J133" t="n">
         <v>190</v>
@@ -4987,34 +4999,34 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.002493446719245879</v>
+        <v>0.002315193692164355</v>
       </c>
       <c r="C134" t="n">
-        <v>0.7385793069394382</v>
+        <v>0.7402076555620216</v>
       </c>
       <c r="D134" t="n">
-        <v>0.153030230148369</v>
+        <v>0.1262796064558003</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.02175307623049582</v>
+        <v>0.003451715102079726</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.02892730569947543</v>
+        <v>-0.0376564639794696</v>
       </c>
       <c r="G134" t="n">
-        <v>0.266715574837365</v>
+        <v>0.2756697000207787</v>
       </c>
       <c r="H134" t="n">
-        <v>-0.1076447299952009</v>
+        <v>-0.1079522131612108</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2632384952490637</v>
+        <v>0.2635843881302589</v>
       </c>
       <c r="J134" t="n">
         <v>190</v>
       </c>
       <c r="K134" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="135">
@@ -5024,28 +5036,28 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.006293101600466955</v>
+        <v>0.006622129717906506</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6250561351493532</v>
+        <v>0.6181546889278977</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.007498279396429665</v>
+        <v>-0.03058426919901958</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.1114693944283547</v>
+        <v>-0.1075914727660054</v>
       </c>
       <c r="F135" t="n">
-        <v>0.04760542493162044</v>
+        <v>0.02980432003896955</v>
       </c>
       <c r="G135" t="n">
-        <v>0.3752447747611599</v>
+        <v>0.3710725726380514</v>
       </c>
       <c r="H135" t="n">
-        <v>0.07106133898265077</v>
+        <v>0.1191441603601063</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3180890937196327</v>
+        <v>0.3197602318475805</v>
       </c>
       <c r="J135" t="n">
         <v>190</v>
@@ -5061,34 +5073,34 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.01204128365328811</v>
+        <v>0.01213763201066384</v>
       </c>
       <c r="C136" t="n">
-        <v>0.5715885654989761</v>
+        <v>0.5738950619636148</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.1338586554626682</v>
+        <v>-0.1214285036638171</v>
       </c>
       <c r="E136" t="n">
-        <v>0.2833130954903461</v>
+        <v>0.3004892133898199</v>
       </c>
       <c r="F136" t="n">
-        <v>0.2612387420805801</v>
+        <v>0.2724072584951688</v>
       </c>
       <c r="G136" t="n">
-        <v>0.5937552417901417</v>
+        <v>0.5993934032447412</v>
       </c>
       <c r="H136" t="n">
-        <v>-0.5760369893973756</v>
+        <v>-0.6247564334295278</v>
       </c>
       <c r="I136" t="n">
-        <v>0.216585215770179</v>
+        <v>0.2213134565667065</v>
       </c>
       <c r="J136" t="n">
         <v>57</v>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -5117,28 +5129,28 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-0.004142504095448878</v>
+        <v>-0.00395559436732472</v>
       </c>
       <c r="C138" t="n">
-        <v>1.048824198275827</v>
+        <v>1.047014204863573</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.6208820283844743</v>
+        <v>-0.5913791750482296</v>
       </c>
       <c r="E138" t="n">
-        <v>0.5402253142757847</v>
+        <v>0.5212709410651392</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.2808735596459074</v>
+        <v>-0.2769235783554235</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2983443355678949</v>
+        <v>0.2929097214278653</v>
       </c>
       <c r="H138" t="n">
-        <v>0.01436173991087501</v>
+        <v>0.007107886047075573</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4929852346501516</v>
+        <v>0.4910821432025689</v>
       </c>
       <c r="J138" t="n">
         <v>81</v>
@@ -5173,34 +5185,34 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.006145681192959566</v>
+        <v>0.00680105165491353</v>
       </c>
       <c r="C140" t="n">
-        <v>0.7134488054981089</v>
+        <v>0.7073661996675689</v>
       </c>
       <c r="D140" t="n">
-        <v>0.08180165964383217</v>
+        <v>0.07290281127575679</v>
       </c>
       <c r="E140" t="n">
-        <v>0.1270790262963444</v>
+        <v>0.1110211576289685</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.1702679731052819</v>
+        <v>-0.1815076889974725</v>
       </c>
       <c r="G140" t="n">
-        <v>0.1973022514783067</v>
+        <v>0.1917351054474859</v>
       </c>
       <c r="H140" t="n">
-        <v>0.05063623018868972</v>
+        <v>0.09848241497769236</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2599852213081477</v>
+        <v>0.2589171370280429</v>
       </c>
       <c r="J140" t="n">
         <v>190</v>
       </c>
       <c r="K140" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -5210,34 +5222,34 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.005881861829839427</v>
+        <v>0.006034368459491301</v>
       </c>
       <c r="C141" t="n">
-        <v>0.8342145729120118</v>
+        <v>0.8350153020591675</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4023516221165847</v>
+        <v>0.4351564951885875</v>
       </c>
       <c r="E141" t="n">
-        <v>0.05818160122457831</v>
+        <v>0.03276014067461107</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.07507866997503995</v>
+        <v>-0.07078339194592864</v>
       </c>
       <c r="G141" t="n">
-        <v>-0.2172580502674255</v>
+        <v>-0.2040723795620849</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.00241107601070946</v>
+        <v>-0.02807616641435248</v>
       </c>
       <c r="I141" t="n">
-        <v>0.5281726242542539</v>
+        <v>0.5335659082839033</v>
       </c>
       <c r="J141" t="n">
         <v>121</v>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="142">
@@ -5266,34 +5278,34 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-0.02109697033626106</v>
+        <v>-0.02447037426043979</v>
       </c>
       <c r="C143" t="n">
-        <v>2.113273129319823</v>
+        <v>2.040797974054334</v>
       </c>
       <c r="D143" t="n">
-        <v>0.8250849635154631</v>
+        <v>0.8088884195116045</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.01687731310219577</v>
+        <v>0.2327228527108638</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.5179149803262577</v>
+        <v>-0.543389410821203</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.8552820843823935</v>
+        <v>-0.7808748292975293</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.5482837150244395</v>
+        <v>-0.7581450061580699</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5168230108496077</v>
+        <v>0.5122124903925536</v>
       </c>
       <c r="J143" t="n">
         <v>24</v>
       </c>
       <c r="K143" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -5303,28 +5315,28 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-0.01084041125628447</v>
+        <v>-0.0115269167149048</v>
       </c>
       <c r="C144" t="n">
-        <v>1.20860918673861</v>
+        <v>1.219955558369464</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.8328996242282117</v>
+        <v>-0.8213230968841859</v>
       </c>
       <c r="E144" t="n">
-        <v>1.00951461516098</v>
+        <v>0.9818899904828144</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2365753306587613</v>
+        <v>0.2257585310076968</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.522757950970307</v>
+        <v>-0.5181922138421228</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.09904155735983219</v>
+        <v>-0.08808876913366681</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4886697656028581</v>
+        <v>0.4900597485277521</v>
       </c>
       <c r="J144" t="n">
         <v>84</v>
@@ -5340,34 +5352,34 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-0.004144007831856995</v>
+        <v>-0.005486935384501975</v>
       </c>
       <c r="C145" t="n">
-        <v>1.391611972712954</v>
+        <v>1.396550010882158</v>
       </c>
       <c r="D145" t="n">
-        <v>0.2641400193800268</v>
+        <v>0.2241734480330452</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.1997327342718238</v>
+        <v>-0.1265590249296064</v>
       </c>
       <c r="F145" t="n">
-        <v>0.2431180571495813</v>
+        <v>0.2478160671252692</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.3281660072673004</v>
+        <v>-0.3153085786111193</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.3709713077034381</v>
+        <v>-0.4266719224997472</v>
       </c>
       <c r="I145" t="n">
-        <v>0.347279804601763</v>
+        <v>0.3472929219626437</v>
       </c>
       <c r="J145" t="n">
         <v>190</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="146">
@@ -5377,28 +5389,28 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-0.01486662530944895</v>
+        <v>-0.01474970280335177</v>
       </c>
       <c r="C146" t="n">
-        <v>0.1766084224370812</v>
+        <v>0.1565103471974207</v>
       </c>
       <c r="D146" t="n">
-        <v>-1.701868752124168</v>
+        <v>-1.692616444317797</v>
       </c>
       <c r="E146" t="n">
-        <v>3.010772953037603</v>
+        <v>3.036557157093796</v>
       </c>
       <c r="F146" t="n">
-        <v>0.4968663016033774</v>
+        <v>0.5026985886257198</v>
       </c>
       <c r="G146" t="n">
-        <v>0.4630217775348265</v>
+        <v>0.4126909333990627</v>
       </c>
       <c r="H146" t="n">
-        <v>-1.445400702488721</v>
+        <v>-1.415840581998202</v>
       </c>
       <c r="I146" t="n">
-        <v>0.4257004124692234</v>
+        <v>0.4543708874662111</v>
       </c>
       <c r="J146" t="n">
         <v>36</v>
@@ -5414,28 +5426,28 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.001773232123258382</v>
+        <v>0.001644713450197908</v>
       </c>
       <c r="C147" t="n">
-        <v>0.8292149494788851</v>
+        <v>0.8227458523844264</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2619481280654011</v>
+        <v>0.2367913472799617</v>
       </c>
       <c r="E147" t="n">
-        <v>0.1851304278606983</v>
+        <v>0.2209749489310736</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.2463269204176902</v>
+        <v>-0.2732162532886658</v>
       </c>
       <c r="G147" t="n">
-        <v>0.01200063520597821</v>
+        <v>0.008466444841550055</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.04196722019327242</v>
+        <v>-0.01576234014834593</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4043517589206351</v>
+        <v>0.4090990770136882</v>
       </c>
       <c r="J147" t="n">
         <v>190</v>
@@ -5451,28 +5463,28 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.002504356302624591</v>
+        <v>0.002450310815145018</v>
       </c>
       <c r="C148" t="n">
-        <v>0.8904871286129278</v>
+        <v>0.8990933930116269</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.303889629454243</v>
+        <v>-0.3090426491776901</v>
       </c>
       <c r="E148" t="n">
-        <v>0.4335437097473811</v>
+        <v>0.4277322423686346</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.2844522364113878</v>
+        <v>-0.2996001307422715</v>
       </c>
       <c r="G148" t="n">
-        <v>0.2088246167578775</v>
+        <v>0.2248798926802184</v>
       </c>
       <c r="H148" t="n">
-        <v>0.05548641074744436</v>
+        <v>0.05693725185948173</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3070909869254422</v>
+        <v>0.3098363127257354</v>
       </c>
       <c r="J148" t="n">
         <v>168</v>
@@ -5488,28 +5500,28 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-0.0008490730999246653</v>
+        <v>2.164642809217947e-05</v>
       </c>
       <c r="C149" t="n">
-        <v>0.7005130019597372</v>
+        <v>0.7208674009778975</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4807503953583729</v>
+        <v>0.58607310096606</v>
       </c>
       <c r="E149" t="n">
-        <v>0.1405339831519645</v>
+        <v>0.05129519421241885</v>
       </c>
       <c r="F149" t="n">
-        <v>0.04994222724558409</v>
+        <v>0.06343168601432475</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.1113454555487286</v>
+        <v>-0.1444683243165855</v>
       </c>
       <c r="H149" t="n">
-        <v>-0.2603941521669301</v>
+        <v>-0.2771990578541157</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2508618577830979</v>
+        <v>0.2645811841444661</v>
       </c>
       <c r="J149" t="n">
         <v>81</v>
@@ -5525,28 +5537,28 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-0.01739019030683401</v>
+        <v>-0.01736345853817282</v>
       </c>
       <c r="C150" t="n">
-        <v>0.9238473610503639</v>
+        <v>0.9220238739947026</v>
       </c>
       <c r="D150" t="n">
-        <v>0.3032864195138067</v>
+        <v>0.2893001299425185</v>
       </c>
       <c r="E150" t="n">
-        <v>0.5058693041710155</v>
+        <v>0.5281988746331998</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.1099332609481001</v>
+        <v>-0.1539612628072132</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.433362304737251</v>
+        <v>-0.411490997990486</v>
       </c>
       <c r="H150" t="n">
-        <v>-0.189707519049835</v>
+        <v>-0.1740706177727216</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4237316800869867</v>
+        <v>0.4244540176893455</v>
       </c>
       <c r="J150" t="n">
         <v>109</v>
@@ -5581,34 +5593,34 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.007919438867825989</v>
+        <v>0.008170800329245326</v>
       </c>
       <c r="C152" t="n">
-        <v>0.4336176468095031</v>
+        <v>0.4354500457988342</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.3189570723716164</v>
+        <v>-0.3296166682250599</v>
       </c>
       <c r="E152" t="n">
-        <v>0.4304878851913637</v>
+        <v>0.4234691491595141</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.3130152711726058</v>
+        <v>-0.3305857739401177</v>
       </c>
       <c r="G152" t="n">
-        <v>0.4425165666016658</v>
+        <v>0.4446857593030012</v>
       </c>
       <c r="H152" t="n">
-        <v>0.3253502449416895</v>
+        <v>0.3565974879038281</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2521116769052523</v>
+        <v>0.2543062283820205</v>
       </c>
       <c r="J152" t="n">
         <v>109</v>
       </c>
       <c r="K152" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -5618,34 +5630,34 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.002253726202678711</v>
+        <v>0.001799822383149303</v>
       </c>
       <c r="C153" t="n">
-        <v>0.9786435319381105</v>
+        <v>0.9963265883593224</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.5682141047852921</v>
+        <v>-0.5828616962062727</v>
       </c>
       <c r="E153" t="n">
-        <v>0.3111880805829397</v>
+        <v>0.3279122120013941</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.05889903804440523</v>
+        <v>-0.05316461614915441</v>
       </c>
       <c r="G153" t="n">
-        <v>0.1303583962921925</v>
+        <v>0.1298284183805143</v>
       </c>
       <c r="H153" t="n">
-        <v>0.2069231340164547</v>
+        <v>0.1819590936141963</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3504693145477715</v>
+        <v>0.3583523841087772</v>
       </c>
       <c r="J153" t="n">
         <v>73</v>
       </c>
       <c r="K153" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -5655,28 +5667,28 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.00371406448470659</v>
+        <v>0.003160879578397524</v>
       </c>
       <c r="C154" t="n">
-        <v>1.145547656648981</v>
+        <v>1.153052199650344</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.5927103683986906</v>
+        <v>-0.5890397319604527</v>
       </c>
       <c r="E154" t="n">
-        <v>0.232407432600606</v>
+        <v>0.2437114312111732</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.3664692344662357</v>
+        <v>-0.3690304991290786</v>
       </c>
       <c r="G154" t="n">
-        <v>0.3629496549966378</v>
+        <v>0.3766545123941785</v>
       </c>
       <c r="H154" t="n">
-        <v>0.2182748586187014</v>
+        <v>0.1846520878338354</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6411215409344847</v>
+        <v>0.6445654241590606</v>
       </c>
       <c r="J154" t="n">
         <v>93</v>
@@ -5711,28 +5723,28 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-0.0006080241759095643</v>
+        <v>-0.0006011290305479806</v>
       </c>
       <c r="C156" t="n">
-        <v>0.9458046431211682</v>
+        <v>0.9471344149593859</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.5535159002968717</v>
+        <v>-0.536911557129928</v>
       </c>
       <c r="E156" t="n">
-        <v>0.4673489313403753</v>
+        <v>0.4553280104464832</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.321376626421456</v>
+        <v>-0.3149733621012567</v>
       </c>
       <c r="G156" t="n">
-        <v>0.4363099362193754</v>
+        <v>0.4214404527703767</v>
       </c>
       <c r="H156" t="n">
-        <v>0.02542901603740888</v>
+        <v>0.02798204105493896</v>
       </c>
       <c r="I156" t="n">
-        <v>0.5419494113147141</v>
+        <v>0.5434371990243358</v>
       </c>
       <c r="J156" t="n">
         <v>84</v>
@@ -5748,28 +5760,28 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.003591577265923868</v>
+        <v>0.003903387316591116</v>
       </c>
       <c r="C157" t="n">
-        <v>0.6222604692130862</v>
+        <v>0.6198673636427572</v>
       </c>
       <c r="D157" t="n">
-        <v>0.2485337714604668</v>
+        <v>0.2479068889233542</v>
       </c>
       <c r="E157" t="n">
-        <v>0.1178365574007605</v>
+        <v>0.1094811926147223</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.2025002041336765</v>
+        <v>-0.2027206020860513</v>
       </c>
       <c r="G157" t="n">
-        <v>0.3546620757925115</v>
+        <v>0.3564305260265602</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.1407926697331485</v>
+        <v>-0.1309653691213426</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3228700773723138</v>
+        <v>0.321793390730866</v>
       </c>
       <c r="J157" t="n">
         <v>190</v>
@@ -5804,34 +5816,34 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-0.001160034462482069</v>
+        <v>-0.0003270850484586594</v>
       </c>
       <c r="C159" t="n">
-        <v>0.9668995778944263</v>
+        <v>0.9612827196808154</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.1670284682173723</v>
+        <v>-0.1258942929883717</v>
       </c>
       <c r="E159" t="n">
-        <v>0.1016661032699203</v>
+        <v>0.03914476360889275</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.07559581292416871</v>
+        <v>-0.05435545251400248</v>
       </c>
       <c r="G159" t="n">
-        <v>0.08837847933261019</v>
+        <v>0.07578407969650651</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0856801206445842</v>
+        <v>0.1040381825161596</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3324852208471114</v>
+        <v>0.3307893892922606</v>
       </c>
       <c r="J159" t="n">
         <v>85</v>
       </c>
       <c r="K159" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -5841,28 +5853,28 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.006079917785533146</v>
+        <v>0.00660051103830698</v>
       </c>
       <c r="C160" t="n">
-        <v>0.8715156404241093</v>
+        <v>0.866657395897811</v>
       </c>
       <c r="D160" t="n">
-        <v>0.08818541197371658</v>
+        <v>0.09420409478991437</v>
       </c>
       <c r="E160" t="n">
-        <v>0.08922689095806864</v>
+        <v>0.07528038529565882</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0102764927032387</v>
+        <v>-2.808767228446724e-05</v>
       </c>
       <c r="G160" t="n">
-        <v>0.2474605454734265</v>
+        <v>0.2389344632177803</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.3066649815325598</v>
+        <v>-0.2750482515288801</v>
       </c>
       <c r="I160" t="n">
-        <v>0.349444749810888</v>
+        <v>0.3455711137316757</v>
       </c>
       <c r="J160" t="n">
         <v>153</v>
@@ -5878,28 +5890,28 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.008388292134641673</v>
+        <v>0.008275262138160487</v>
       </c>
       <c r="C161" t="n">
-        <v>0.9451247083022662</v>
+        <v>0.9520409813321044</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.4377354578610665</v>
+        <v>-0.4323334016341085</v>
       </c>
       <c r="E161" t="n">
-        <v>0.124426977263212</v>
+        <v>0.1182446880175634</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.1898170672824191</v>
+        <v>-0.1785437899069487</v>
       </c>
       <c r="G161" t="n">
-        <v>0.3229226769342178</v>
+        <v>0.3399757673884649</v>
       </c>
       <c r="H161" t="n">
-        <v>0.2350781626437895</v>
+        <v>0.2006157548029247</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3622058428523239</v>
+        <v>0.3625075411248082</v>
       </c>
       <c r="J161" t="n">
         <v>153</v>
@@ -5915,34 +5927,34 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.01367692471153041</v>
+        <v>0.0144296544178037</v>
       </c>
       <c r="C162" t="n">
-        <v>0.7783501352901333</v>
+        <v>0.7575666632427619</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.1399939211653264</v>
+        <v>-0.08351107127231061</v>
       </c>
       <c r="E162" t="n">
-        <v>0.5133203071682929</v>
+        <v>0.4611774724531241</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.286563018510425</v>
+        <v>-0.2641806848994039</v>
       </c>
       <c r="G162" t="n">
-        <v>0.6543887545657553</v>
+        <v>0.597537456916309</v>
       </c>
       <c r="H162" t="n">
-        <v>-0.5195022573484301</v>
+        <v>-0.4685898364404805</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3638759050960521</v>
+        <v>0.345179440862159</v>
       </c>
       <c r="J162" t="n">
         <v>48</v>
       </c>
       <c r="K162" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -5971,28 +5983,28 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.01066130276087948</v>
+        <v>0.01063290855008652</v>
       </c>
       <c r="C164" t="n">
-        <v>1.885939115483194</v>
+        <v>1.913333063368855</v>
       </c>
       <c r="D164" t="n">
-        <v>0.02567246935697615</v>
+        <v>0.2417393964736444</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.9232641646944098</v>
+        <v>-1.130108959382641</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.05068278231279273</v>
+        <v>-0.006657290516157682</v>
       </c>
       <c r="G164" t="n">
-        <v>-0.4245807924723621</v>
+        <v>-0.4965204533411164</v>
       </c>
       <c r="H164" t="n">
-        <v>0.4869161546393949</v>
+        <v>0.4782142433974152</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3149389172399526</v>
+        <v>0.3150580443016742</v>
       </c>
       <c r="J164" t="n">
         <v>69</v>
@@ -6008,34 +6020,34 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-0.005785384961794505</v>
+        <v>-0.005996578708672147</v>
       </c>
       <c r="C165" t="n">
-        <v>1.05214540837098</v>
+        <v>1.046516697588855</v>
       </c>
       <c r="D165" t="n">
-        <v>0.1574757043909742</v>
+        <v>0.1341491900520068</v>
       </c>
       <c r="E165" t="n">
-        <v>0.3340259917076414</v>
+        <v>0.3643495137732905</v>
       </c>
       <c r="F165" t="n">
-        <v>0.1971284994539461</v>
+        <v>0.1914590185886487</v>
       </c>
       <c r="G165" t="n">
-        <v>-0.2779923118893003</v>
+        <v>-0.2765228365264671</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.4627832920342419</v>
+        <v>-0.4599515834763337</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4998038978345314</v>
+        <v>0.4999972111158058</v>
       </c>
       <c r="J165" t="n">
         <v>190</v>
       </c>
       <c r="K165" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="166">
@@ -6045,34 +6057,34 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-0.0172784145086788</v>
+        <v>-0.01553195509038348</v>
       </c>
       <c r="C166" t="n">
-        <v>1.450646641090362</v>
+        <v>1.460937148716779</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.981782211847294</v>
+        <v>-0.8691383642748277</v>
       </c>
       <c r="E166" t="n">
-        <v>0.5751728787163095</v>
+        <v>0.5002657869728337</v>
       </c>
       <c r="F166" t="n">
-        <v>0.08259649054196201</v>
+        <v>0.1283656100101824</v>
       </c>
       <c r="G166" t="n">
-        <v>0.7595461064617697</v>
+        <v>0.7560844792856001</v>
       </c>
       <c r="H166" t="n">
-        <v>-0.8861799049631093</v>
+        <v>-0.9765146607105677</v>
       </c>
       <c r="I166" t="n">
-        <v>0.310814464533653</v>
+        <v>0.2991288896285142</v>
       </c>
       <c r="J166" t="n">
         <v>33</v>
       </c>
       <c r="K166" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -6082,28 +6094,28 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.009546000525480205</v>
+        <v>0.009478661525663533</v>
       </c>
       <c r="C167" t="n">
-        <v>0.7101299357393924</v>
+        <v>0.7099410461840024</v>
       </c>
       <c r="D167" t="n">
-        <v>0.2541174334446577</v>
+        <v>0.2259445270821839</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.1286221139069159</v>
+        <v>-0.1048841867219054</v>
       </c>
       <c r="F167" t="n">
-        <v>0.202206634352345</v>
+        <v>0.1916395238550627</v>
       </c>
       <c r="G167" t="n">
-        <v>0.09883067806046454</v>
+        <v>0.0955590621891335</v>
       </c>
       <c r="H167" t="n">
-        <v>-0.1366625676899437</v>
+        <v>-0.1181999725884772</v>
       </c>
       <c r="I167" t="n">
-        <v>0.16566285043349</v>
+        <v>0.162634816000345</v>
       </c>
       <c r="J167" t="n">
         <v>190</v>
@@ -6119,28 +6131,28 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.002656547304224387</v>
+        <v>0.002215665574004312</v>
       </c>
       <c r="C168" t="n">
-        <v>0.9354687834233436</v>
+        <v>0.9420662050343085</v>
       </c>
       <c r="D168" t="n">
-        <v>0.1465554539925292</v>
+        <v>0.1277361574392525</v>
       </c>
       <c r="E168" t="n">
-        <v>0.1054231629183972</v>
+        <v>0.1307273837640869</v>
       </c>
       <c r="F168" t="n">
-        <v>-0.1519495704420642</v>
+        <v>-0.1569931302725401</v>
       </c>
       <c r="G168" t="n">
-        <v>-0.01997561528318856</v>
+        <v>-0.009812452805280723</v>
       </c>
       <c r="H168" t="n">
-        <v>-0.01552221460901728</v>
+        <v>-0.03372416315982707</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4679198870904958</v>
+        <v>0.4674080173468259</v>
       </c>
       <c r="J168" t="n">
         <v>190</v>
@@ -6156,34 +6168,34 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-0.0008295062166137176</v>
+        <v>-0.001208507764277569</v>
       </c>
       <c r="C169" t="n">
-        <v>1.029259905328803</v>
+        <v>1.037250708611195</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.2809224778075415</v>
+        <v>-0.2747703410739704</v>
       </c>
       <c r="E169" t="n">
-        <v>0.1584576528336649</v>
+        <v>0.1549080142751763</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.3317051563268982</v>
+        <v>-0.3140920314354543</v>
       </c>
       <c r="G169" t="n">
-        <v>0.1455215153662891</v>
+        <v>0.1519955069844116</v>
       </c>
       <c r="H169" t="n">
-        <v>0.2793885606056833</v>
+        <v>0.2447081426386416</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4244767332113463</v>
+        <v>0.423098386258278</v>
       </c>
       <c r="J169" t="n">
         <v>169</v>
       </c>
       <c r="K169" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -6193,34 +6205,34 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.005244412380301909</v>
+        <v>0.006121814410961496</v>
       </c>
       <c r="C170" t="n">
-        <v>0.7736780498485701</v>
+        <v>0.7652952281026825</v>
       </c>
       <c r="D170" t="n">
-        <v>0.3103029007775886</v>
+        <v>0.3245093444039243</v>
       </c>
       <c r="E170" t="n">
-        <v>0.06797737261099288</v>
+        <v>0.02454952597521027</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.1980143730444705</v>
+        <v>-0.1924644016952891</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.07614048067257541</v>
+        <v>-0.08175568692764598</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1221965304798943</v>
+        <v>0.159865990141118</v>
       </c>
       <c r="I170" t="n">
-        <v>0.5032152108900214</v>
+        <v>0.5098656161264241</v>
       </c>
       <c r="J170" t="n">
         <v>121</v>
       </c>
       <c r="K170" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="171">
@@ -6230,28 +6242,28 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.005589461951095409</v>
+        <v>0.005739268618108534</v>
       </c>
       <c r="C171" t="n">
-        <v>0.96015175908511</v>
+        <v>0.9564974484193557</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.2757080011572658</v>
+        <v>-0.2692790478240278</v>
       </c>
       <c r="E171" t="n">
-        <v>0.2779870713649552</v>
+        <v>0.2739791291855532</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.1203295300227026</v>
+        <v>-0.1176780797971833</v>
       </c>
       <c r="G171" t="n">
-        <v>0.2538215271325812</v>
+        <v>0.2510137346108053</v>
       </c>
       <c r="H171" t="n">
-        <v>-0.09592282640267799</v>
+        <v>-0.09453318459450311</v>
       </c>
       <c r="I171" t="n">
-        <v>0.4546108050397353</v>
+        <v>0.4542638498728484</v>
       </c>
       <c r="J171" t="n">
         <v>190</v>
@@ -6286,34 +6298,34 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.005401216840212415</v>
+        <v>0.004794993417033485</v>
       </c>
       <c r="C173" t="n">
-        <v>0.3546492814869144</v>
+        <v>0.3635435350024598</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.3286436976939822</v>
+        <v>-0.3248113271117871</v>
       </c>
       <c r="E173" t="n">
-        <v>0.8143632453018522</v>
+        <v>0.8198249202973733</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.1804535071893787</v>
+        <v>-0.1753095430696786</v>
       </c>
       <c r="G173" t="n">
-        <v>-0.008011168225377249</v>
+        <v>-0.004421856616077469</v>
       </c>
       <c r="H173" t="n">
-        <v>0.3480958463199715</v>
+        <v>0.3211742714977099</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1524666499060734</v>
+        <v>0.1521241085139524</v>
       </c>
       <c r="J173" t="n">
         <v>57</v>
       </c>
       <c r="K173" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -6323,28 +6335,28 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.003747729865769186</v>
+        <v>0.003999809239859383</v>
       </c>
       <c r="C174" t="n">
-        <v>0.5012990579241985</v>
+        <v>0.4984673463105049</v>
       </c>
       <c r="D174" t="n">
-        <v>0.01677895022210617</v>
+        <v>0.004542054591704342</v>
       </c>
       <c r="E174" t="n">
-        <v>0.1986760084416269</v>
+        <v>0.2015412730270981</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.1060449966838962</v>
+        <v>-0.1147874195781291</v>
       </c>
       <c r="G174" t="n">
-        <v>0.3358313179779164</v>
+        <v>0.332330293709544</v>
       </c>
       <c r="H174" t="n">
-        <v>0.05345966211804822</v>
+        <v>0.07790645193927766</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2274216663150324</v>
+        <v>0.2227987015064644</v>
       </c>
       <c r="J174" t="n">
         <v>190</v>
@@ -6394,69 +6406,69 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.008503622238559562</v>
+        <v>0.002600316382588764</v>
       </c>
       <c r="C177" t="n">
-        <v>0.6395005539883283</v>
+        <v>0.9428600949533519</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.05777340798127364</v>
+        <v>0.7187171339993698</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.05255817922094604</v>
+        <v>-0.2842019685040835</v>
       </c>
       <c r="F177" t="n">
-        <v>0.1476764522383953</v>
+        <v>-0.03219792879999228</v>
       </c>
       <c r="G177" t="n">
-        <v>0.347905778840236</v>
+        <v>-0.2128253467314702</v>
       </c>
       <c r="H177" t="n">
-        <v>-0.02475119786473986</v>
+        <v>-0.1323519849171756</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2260346253069019</v>
+        <v>0.5006050840208295</v>
       </c>
       <c r="J177" t="n">
         <v>190</v>
       </c>
       <c r="K177" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.001131337656169047</v>
+        <v>0.008675490620899444</v>
       </c>
       <c r="C178" t="n">
-        <v>0.7182386343595374</v>
+        <v>0.627521798818412</v>
       </c>
       <c r="D178" t="n">
-        <v>0.6034265210638464</v>
+        <v>-0.07118204915866491</v>
       </c>
       <c r="E178" t="n">
-        <v>0.0869899593268037</v>
+        <v>-0.03865913546165782</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.1672420149935109</v>
+        <v>0.1230433463003157</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.002708073611644031</v>
+        <v>0.3399440789397351</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.2387050261450326</v>
+        <v>0.01933196056185994</v>
       </c>
       <c r="I178" t="n">
-        <v>0.384083546433683</v>
+        <v>0.2261768961555165</v>
       </c>
       <c r="J178" t="n">
         <v>190</v>
@@ -6468,37 +6480,74 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0.001026295799297087</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.7113265056766696</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.589983368193661</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.1150361734262045</v>
+      </c>
+      <c r="F179" t="n">
+        <v>-0.1727544175372542</v>
+      </c>
+      <c r="G179" t="n">
+        <v>-0.01025569212772187</v>
+      </c>
+      <c r="H179" t="n">
+        <v>-0.2333359376315589</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0.3857067673646229</v>
+      </c>
+      <c r="J179" t="n">
+        <v>190</v>
+      </c>
+      <c r="K179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
           <t>ZTS</t>
         </is>
       </c>
-      <c r="B179" t="n">
-        <v>0.006065866193829932</v>
-      </c>
-      <c r="C179" t="n">
-        <v>0.9798473158895894</v>
-      </c>
-      <c r="D179" t="n">
-        <v>-0.7283090224014593</v>
-      </c>
-      <c r="E179" t="n">
-        <v>0.3258477049085838</v>
-      </c>
-      <c r="F179" t="n">
-        <v>-0.143052516989349</v>
-      </c>
-      <c r="G179" t="n">
-        <v>0.4575028240307461</v>
-      </c>
-      <c r="H179" t="n">
-        <v>0.1081636945618891</v>
-      </c>
-      <c r="I179" t="n">
-        <v>0.5748306296645369</v>
-      </c>
-      <c r="J179" t="n">
+      <c r="B180" t="n">
+        <v>0.005497429682367189</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.9799315636465243</v>
+      </c>
+      <c r="D180" t="n">
+        <v>-0.6941980426036748</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.3160469145051368</v>
+      </c>
+      <c r="F180" t="n">
+        <v>-0.134347841066946</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.4425465339532561</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.09002087156570354</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0.5756741124836195</v>
+      </c>
+      <c r="J180" t="n">
         <v>60</v>
       </c>
-      <c r="K179" t="n">
+      <c r="K180" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6517,12 +6566,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>concepto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>definición</t>
         </is>
